--- a/DATA/antigen_CI_Random_generator.xlsx
+++ b/DATA/antigen_CI_Random_generator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="493" documentId="11_4A5645C871AEA98286DE389EAFF8EF0F542BC54D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B636E8DF-CC19-4AC8-BDB6-B605B9E02EA1}"/>
+  <xr:revisionPtr revIDLastSave="590" documentId="11_4A5645C871AEA98286DE389EAFF8EF0F542BC54D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2937F37B-86E6-431C-A5C2-8E05EA8207B0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="17">
   <si>
     <t>Lower</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>PCV</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
@@ -333,34 +336,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>247987687.94228613</c:v>
+                  <c:v>610366749.10346115</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>510707011.35090262</c:v>
+                  <c:v>531163244.01083982</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>779187588.44929445</c:v>
+                  <c:v>799734080.94260573</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>856320288.8265897</c:v>
+                  <c:v>582478519.84207511</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>609012423.49302292</c:v>
+                  <c:v>585579461.66020167</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1143241091.3296049</c:v>
+                  <c:v>795043869.14612949</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>995456032.3599751</c:v>
+                  <c:v>777274926.59863842</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>842337190.69581425</c:v>
+                  <c:v>812112294.92690504</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1383348569.0750978</c:v>
+                  <c:v>916431319.59162045</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1017644951.862873</c:v>
+                  <c:v>788606590.24584341</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -405,34 +408,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>39449727.696229212</c:v>
+                  <c:v>20151026.863962889</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22092075.843436118</c:v>
+                  <c:v>25356646.942508951</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14054469.562461421</c:v>
+                  <c:v>27543029.649350435</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>58850113.188332558</c:v>
+                  <c:v>37009863.591849729</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>26097197.900835525</c:v>
+                  <c:v>36017326.664739236</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>34164435.01032491</c:v>
+                  <c:v>41641280.211628623</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>85093245.656676412</c:v>
+                  <c:v>38600796.984534249</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>28777382.649661399</c:v>
+                  <c:v>46346411.309301585</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>20864361.672251873</c:v>
+                  <c:v>52122361.570719413</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>70486241.419496059</c:v>
+                  <c:v>63584922.777330749</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -477,34 +480,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>190948844.07116279</c:v>
+                  <c:v>269979741.65914881</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>267844914.35984373</c:v>
+                  <c:v>424620184.82685202</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>197265695.85591027</c:v>
+                  <c:v>458445881.5196749</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>689555343.34359598</c:v>
+                  <c:v>441303051.16330719</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>935183993.09773898</c:v>
+                  <c:v>518738648.8944546</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>825663716.02607489</c:v>
+                  <c:v>560590321.12412798</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>476314964.47713357</c:v>
+                  <c:v>619263506.51350164</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>288335650.59274518</c:v>
+                  <c:v>597953201.04888475</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>783705380.60791039</c:v>
+                  <c:v>741556488.15382314</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1000029267.9655296</c:v>
+                  <c:v>763885830.22618496</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -549,34 +552,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>777076702.64843607</c:v>
+                  <c:v>742785491.46924627</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>760581543.52950549</c:v>
+                  <c:v>752853587.4273622</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>808863065.2732867</c:v>
+                  <c:v>846484448.36472392</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>437709524.92591959</c:v>
+                  <c:v>911331567.75979292</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>938140151.90137815</c:v>
+                  <c:v>904479481.78190124</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1249538752.1930645</c:v>
+                  <c:v>1164816092.3500228</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>936954635.58204234</c:v>
+                  <c:v>1458084052.6528018</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1058037518.6819162</c:v>
+                  <c:v>1527318076.5038919</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1087653563.6034088</c:v>
+                  <c:v>1591242235.5884593</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1665762716.9262967</c:v>
+                  <c:v>1920616477.7595139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -621,34 +624,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>570605073.91759527</c:v>
+                  <c:v>602773484.32235479</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>546556435.55415082</c:v>
+                  <c:v>640837760.7040205</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>718816673.81974113</c:v>
+                  <c:v>685019527.58840501</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>616884565.48521125</c:v>
+                  <c:v>628349818.47549438</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>743327803.48039961</c:v>
+                  <c:v>641662353.09790337</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>679547072.95331299</c:v>
+                  <c:v>679487017.55810404</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>649080688.50381494</c:v>
+                  <c:v>652578957.22678268</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>621232258.92640686</c:v>
+                  <c:v>663703060.87461042</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>723496931.8686372</c:v>
+                  <c:v>691493859.20329762</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>510073742.07704681</c:v>
+                  <c:v>652692515.10939085</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -693,34 +696,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>349521208.98853433</c:v>
+                  <c:v>362422627.99443895</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>418726778.96281028</c:v>
+                  <c:v>315701250.17060524</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>414506121.0054183</c:v>
+                  <c:v>368472445.85273087</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>389086827.05914652</c:v>
+                  <c:v>317119649.02451921</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>328572142.56714904</c:v>
+                  <c:v>376239025.84218717</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>433502559.49073392</c:v>
+                  <c:v>374412379.16049558</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>301740966.09930253</c:v>
+                  <c:v>356424154.96221793</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>315575726.75245166</c:v>
+                  <c:v>387528371.29742432</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>440707781.5308395</c:v>
+                  <c:v>357256293.51931</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>233020369.69882864</c:v>
+                  <c:v>350848044.49634397</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -767,34 +770,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>384895186.13944066</c:v>
+                  <c:v>395303027.42456394</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>494109545.4175849</c:v>
+                  <c:v>408220393.14708143</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>551227913.124102</c:v>
+                  <c:v>444641915.07728684</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>367170060.14926147</c:v>
+                  <c:v>453827503.85857785</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>367887653.91808963</c:v>
+                  <c:v>383013545.72927064</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>315906475.65011495</c:v>
+                  <c:v>379502006.21421438</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>201180556.01515657</c:v>
+                  <c:v>401255114.97082168</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>686135126.50546062</c:v>
+                  <c:v>444774444.58579254</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>403934581.52783585</c:v>
+                  <c:v>403463446.28985393</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>619312530.39886892</c:v>
+                  <c:v>467796355.77015615</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -841,34 +844,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>335380421.76351452</c:v>
+                  <c:v>314257258.63745034</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>338107043.03026891</c:v>
+                  <c:v>314152799.93181235</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>266697082.57227737</c:v>
+                  <c:v>350041789.64064449</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>306958981.54394561</c:v>
+                  <c:v>301268334.68733639</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>382015773.38942373</c:v>
+                  <c:v>352128748.55086374</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>344414358.96267444</c:v>
+                  <c:v>355668888.58184254</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>342642948.07313633</c:v>
+                  <c:v>398675396.96262902</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>362039763.82889336</c:v>
+                  <c:v>427391965.79788744</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>314379291.95968014</c:v>
+                  <c:v>352020151.85880196</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>447264457.43530977</c:v>
+                  <c:v>434381232.9750579</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -915,34 +918,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>716469135.2208643</c:v>
+                  <c:v>562510067.91676295</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>534554254.60230482</c:v>
+                  <c:v>686050307.64316642</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>737816468.55611467</c:v>
+                  <c:v>575413534.3232224</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>546602869.04926336</c:v>
+                  <c:v>687383594.87407196</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>683420219.39665222</c:v>
+                  <c:v>697755472.33727348</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>628511301.666255</c:v>
+                  <c:v>780317577.12405515</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>941933493.99268901</c:v>
+                  <c:v>749736107.30519927</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>970662569.8041985</c:v>
+                  <c:v>870930380.34278071</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>882526023.78850722</c:v>
+                  <c:v>907526188.16005743</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>923352564.87766623</c:v>
+                  <c:v>892368067.98188782</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -989,34 +992,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>29217931.001447797</c:v>
+                  <c:v>29375908.204356764</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32672389.333723851</c:v>
+                  <c:v>36973240.974811286</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35258738.193920977</c:v>
+                  <c:v>42810635.44118131</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>42905179.298752442</c:v>
+                  <c:v>46450943.908866525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>57101509.13748049</c:v>
+                  <c:v>55751458.96213802</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51936787.984526694</c:v>
+                  <c:v>58567348.47724364</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>61497449.02119904</c:v>
+                  <c:v>67149671.127208233</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>70092761.038888514</c:v>
+                  <c:v>71955815.934473842</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>77539450.587859347</c:v>
+                  <c:v>81054530.296169713</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>89725949.308253497</c:v>
+                  <c:v>89313131.797970936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1063,34 +1066,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>239577204.00124341</c:v>
+                  <c:v>225177168.58647105</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>136461943.51271439</c:v>
+                  <c:v>211818559.40818676</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>265335387.09170458</c:v>
+                  <c:v>197255863.65012899</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>322737358.79651904</c:v>
+                  <c:v>292473628.34834433</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>437375982.26865387</c:v>
+                  <c:v>338275388.45804477</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>430995369.69622892</c:v>
+                  <c:v>381248305.86100721</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>277857332.80848122</c:v>
+                  <c:v>444205575.87645489</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>394733238.23752886</c:v>
+                  <c:v>529896172.87651294</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>639274118.27673209</c:v>
+                  <c:v>663705067.16484177</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>722629654.12376082</c:v>
+                  <c:v>735092352.48062396</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1137,34 +1140,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>242922527.79350901</c:v>
+                  <c:v>241071149.45158824</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>208856647.25570789</c:v>
+                  <c:v>254015380.07613316</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>363423456.81929737</c:v>
+                  <c:v>290306034.27144468</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>235745910.90144414</c:v>
+                  <c:v>306939644.52600533</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>196188626.11846769</c:v>
+                  <c:v>336686422.01807326</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>243264208.43181372</c:v>
+                  <c:v>369304271.70029795</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>359744862.80326867</c:v>
+                  <c:v>410655800.2244851</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>330044939.63516736</c:v>
+                  <c:v>442999496.19893312</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>515014051.08443564</c:v>
+                  <c:v>475584022.34082985</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>340189047.04077357</c:v>
+                  <c:v>454731642.6732856</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2264,161 +2267,187 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>545886518.23867655</v>
       </c>
       <c r="B2">
         <v>777076702.64843607</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>661481610.44355631</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>58977087.859632529</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>508228721.08986032</v>
       </c>
       <c r="B3">
         <v>902179583.3433063</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>705204152.21658325</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>100497668.94220564</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>472845159.87652242</v>
       </c>
       <c r="B4">
         <v>1048139752.510308</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>760492456.19341516</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>146758824.65147597</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>437709524.92591959</v>
       </c>
       <c r="B5">
         <v>1223877877.9551761</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>830793701.44054782</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>200553151.28297362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>402698196.9396286</v>
       </c>
       <c r="B6">
         <v>1437905479.398587</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>920301838.16910779</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>264083490.42320368</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>368115323.15745407</v>
       </c>
       <c r="B7">
         <v>1700247205.047471</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>1034181264.1024625</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>339829561.70663702</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>334354354.94743532</v>
       </c>
       <c r="B8">
         <v>2023368211.8516331</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>1178861283.3995342</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>430870881.86331576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>301789669.78195262</v>
       </c>
       <c r="B9">
         <v>2423056152.5270262</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>1362422911.1544895</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>541139408.8635391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>270737783.37456232</v>
       </c>
       <c r="B10">
         <v>2919476079.8360252</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>1595106931.6052938</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>675698545.01567936</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>241444983.2206544</v>
       </c>
       <c r="B11">
         <v>3538519113.1622062</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>1889982048.1914303</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>388381023.55526656</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>1799384615.8280175</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>841090339.27080405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>1093882819.6916423</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>359949895.98794651</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2427,161 +2456,187 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>313064095.43054122</v>
       </c>
       <c r="B2">
         <v>449867903.82097661</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>381465999.62575889</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>34898930.711845778</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>284172162.19225121</v>
       </c>
       <c r="B3">
         <v>494109545.4175849</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>389140853.80491805</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>53555454.904421858</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>236929106.38589969</v>
       </c>
       <c r="B4">
         <v>551227913.124102</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>394078509.75500083</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>80178267.025051624</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>204226774.46613339</v>
       </c>
       <c r="B5">
         <v>593697094.67696595</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>398961934.57154965</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>99354673.523171589</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>178608432.22487739</v>
       </c>
       <c r="B6">
         <v>628975015.5441829</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>403791723.88453013</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>114889434.52023101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>157442189.9524743</v>
       </c>
       <c r="B7">
         <v>659694743.61152732</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>408568466.78200078</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>128125651.443636</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>139425132.9823041</v>
       </c>
       <c r="B8">
         <v>687160358.78162241</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>413292745.88196325</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>139728373.92839754</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>123796046.04026081</v>
       </c>
       <c r="B9">
         <v>712134228.76658809</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>417965137.40342444</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>150086271.10365492</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>110062834.5576396</v>
       </c>
       <c r="B10">
         <v>735109587.91571593</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>422586211.23667777</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>159450702.38726437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>97884695.500129983</v>
       </c>
       <c r="B11">
         <v>756428366.52549577</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>427156531.01281285</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>184561146.97325116</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>626840475.8184762</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>167995834.4452464</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>405700811.39586365</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>112826359.39929211</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2590,143 +2645,184 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>263149726.4973551</v>
       </c>
       <c r="B2">
         <v>335380421.76351452</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>299265074.13043481</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>18426197.771979444</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>260202444.8283492</v>
       </c>
       <c r="B3">
         <v>362352073.69339001</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>311277259.26086962</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>26058578.79210224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>260735827.35779801</v>
       </c>
       <c r="B4">
         <v>385843061.42481089</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>323289444.39130443</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>31915110.731380843</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>263070934.2555798</v>
       </c>
       <c r="B5">
         <v>407532324.78789872</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>335301629.52173924</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>36852395.543958917</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>266557442.3135716</v>
       </c>
       <c r="B6">
         <v>428070186.99077648</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>347313814.65217406</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>41202230.785001241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>270861826.19833142</v>
       </c>
       <c r="B7">
         <v>447790173.36688638</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>359325999.78260887</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>45134782.440957911</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>275785956.5632695</v>
       </c>
       <c r="B8">
         <v>466890413.26281792</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>371338184.91304374</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>48751136.913150094</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>281200741.17843771</v>
       </c>
       <c r="B9">
         <v>485499998.90851933</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>383350370.04347849</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52117157.58420451</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>287016512.27467412</v>
       </c>
       <c r="B10">
         <v>503708598.07315248</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>395362555.1739133</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>55278593.315938361</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>293167983.29504508</v>
       </c>
       <c r="B11">
         <v>521581497.31365108</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>407374740.30434811</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>58268753.576174989</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f>AVERAGE(A2:A11)</f>
         <v>272174939.47624111</v>
@@ -2735,15 +2831,9 @@
         <f>AVERAGE(B2:B11)</f>
         <v>434464874.95854175</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
+      <c r="C13" s="4">
+        <f>AVERAGE(C2:C11)</f>
         <v>353319907.21739149</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>41400493.745484829</v>
       </c>
     </row>
   </sheetData>
@@ -2753,161 +2843,187 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25915770.51731832</v>
       </c>
       <c r="B2">
         <v>31963266.345840931</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>28939518.431579627</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>1542728.5276843386</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>32672389.333723851</v>
       </c>
       <c r="B3">
         <v>39307452.706052743</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>35989921.019888297</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>1692618.2072267584</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>35258738.193920977</v>
       </c>
       <c r="B4">
         <v>46720358.840827107</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>40989548.517374039</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>2923882.8180883005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>39200401.038449273</v>
       </c>
       <c r="B5">
         <v>52982966.643657863</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>46091683.841053568</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>3515960.6135736201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>44801882.931156076</v>
       </c>
       <c r="B6">
         <v>62638826.957431652</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>53720354.944293864</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>4550240.8230294837</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>47468482.931389228</v>
       </c>
       <c r="B7">
         <v>69521043.214136243</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>58494763.072762735</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>5625653.1333538303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>53936392.052826867</v>
       </c>
       <c r="B8">
         <v>79895884.902370557</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>66916138.477598712</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>6622319.6044754311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>57364080.2476006</v>
       </c>
       <c r="B9">
         <v>88600252.548571095</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>72982166.398085847</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>7968411.3012679834</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>63252402.675496884</v>
       </c>
       <c r="B10">
         <v>98899565.376091331</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>81075984.025794104</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>9093663.9542332795</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>68321695.588667631</v>
       </c>
       <c r="B11">
         <v>109568223.25169291</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>88944959.420180261</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>46819223.551054969</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>68009784.078667253</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>10522073.383424819</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>57414503.814861104</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>5405755.2366357902</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2963,44 +3079,44 @@
         <v>4</v>
       </c>
       <c r="B2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D2,Measles!$F$13)</f>
-        <v>247987687.94228613</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C2,Measles!$D$2)</f>
+        <v>610366749.10346115</v>
       </c>
       <c r="C2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D3,Measles!$F$13)</f>
-        <v>510707011.35090262</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C3,Measles!$D$2)</f>
+        <v>531163244.01083982</v>
       </c>
       <c r="D2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D4,Measles!$F$13)</f>
-        <v>779187588.44929445</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C4,Measles!$D$2)</f>
+        <v>799734080.94260573</v>
       </c>
       <c r="E2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D5,Measles!$F$13)</f>
-        <v>856320288.8265897</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C5,Measles!$D$2)</f>
+        <v>582478519.84207511</v>
       </c>
       <c r="F2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D6,Measles!$F$13)</f>
-        <v>609012423.49302292</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C6,Measles!$D$2)</f>
+        <v>585579461.66020167</v>
       </c>
       <c r="G2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D7,Measles!$F$13)</f>
-        <v>1143241091.3296049</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C7,Measles!$D$2)</f>
+        <v>795043869.14612949</v>
       </c>
       <c r="H2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D8,Measles!$F$13)</f>
-        <v>995456032.3599751</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C8,Measles!$D$2)</f>
+        <v>777274926.59863842</v>
       </c>
       <c r="I2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D9,Measles!$F$13)</f>
-        <v>842337190.69581425</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C9,Measles!$D$2)</f>
+        <v>812112294.92690504</v>
       </c>
       <c r="J2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D10,Measles!$F$13)</f>
-        <v>1383348569.0750978</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C10,Measles!$D$2)</f>
+        <v>916431319.59162045</v>
       </c>
       <c r="K2" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D11,Measles!$F$13)</f>
-        <v>1017644951.862873</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C11,Measles!$D$2)</f>
+        <v>788606590.24584341</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -3008,44 +3124,44 @@
         <v>5</v>
       </c>
       <c r="B3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D2,Mumps!$F$13)</f>
-        <v>58875697.922735527</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C2,Mumps!$D$2)</f>
+        <v>20151026.863962889</v>
       </c>
       <c r="C3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D3,Mumps!$F$13)</f>
-        <v>22092075.843436118</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C3,Mumps!$D$2)</f>
+        <v>25356646.942508951</v>
       </c>
       <c r="D3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D4,Mumps!$F$13)</f>
-        <v>14054469.562461421</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C4,Mumps!$D$2)</f>
+        <v>27543029.649350435</v>
       </c>
       <c r="E3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D5,Mumps!$F$13)</f>
-        <v>58850113.188332558</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C5,Mumps!$D$2)</f>
+        <v>37009863.591849729</v>
       </c>
       <c r="F3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D6,Mumps!$F$13)</f>
-        <v>26097197.900835525</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C6,Mumps!$D$2)</f>
+        <v>36017326.664739236</v>
       </c>
       <c r="G3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D7,Mumps!$F$13)</f>
-        <v>34164435.01032491</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C7,Mumps!$D$2)</f>
+        <v>41641280.211628623</v>
       </c>
       <c r="H3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D8,Mumps!$F$13)</f>
-        <v>85093245.656676412</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C8,Mumps!$D$2)</f>
+        <v>38600796.984534249</v>
       </c>
       <c r="I3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D9,Mumps!$F$13)</f>
-        <v>28777382.649661399</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C9,Mumps!$D$2)</f>
+        <v>46346411.309301585</v>
       </c>
       <c r="J3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D10,Mumps!$F$13)</f>
-        <v>20864361.672251873</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C10,Mumps!$D$2)</f>
+        <v>52122361.570719413</v>
       </c>
       <c r="K3" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D11,Mumps!$F$13)</f>
-        <v>70486241.419496059</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C11,Mumps!$D$2)</f>
+        <v>63584922.777330749</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -3053,44 +3169,44 @@
         <v>6</v>
       </c>
       <c r="B4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D2,Rubella!$F$13)</f>
-        <v>-50718149.264266491</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C2,Rubella!$D$2)</f>
+        <v>269979741.65914881</v>
       </c>
       <c r="C4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D3,Rubella!$F$13)</f>
-        <v>267844914.35984373</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C3,Rubella!$D$2)</f>
+        <v>424620184.82685202</v>
       </c>
       <c r="D4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D4,Rubella!$F$13)</f>
-        <v>197265695.85591027</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C4,Rubella!$D$2)</f>
+        <v>458445881.5196749</v>
       </c>
       <c r="E4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D5,Rubella!$F$13)</f>
-        <v>689555343.34359598</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C5,Rubella!$D$2)</f>
+        <v>441303051.16330719</v>
       </c>
       <c r="F4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D6,Rubella!$F$13)</f>
-        <v>949635225.20630527</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C6,Rubella!$D$2)</f>
+        <v>518738648.8944546</v>
       </c>
       <c r="G4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D7,Rubella!$F$13)</f>
-        <v>825663716.02607489</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C7,Rubella!$D$2)</f>
+        <v>560590321.12412798</v>
       </c>
       <c r="H4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D8,Rubella!$F$13)</f>
-        <v>476314964.47713357</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C8,Rubella!$D$2)</f>
+        <v>619263506.51350164</v>
       </c>
       <c r="I4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D9,Rubella!$F$13)</f>
-        <v>288335650.59274518</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C9,Rubella!$D$2)</f>
+        <v>597953201.04888475</v>
       </c>
       <c r="J4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D10,Rubella!$F$13)</f>
-        <v>783705380.60791039</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C10,Rubella!$D$2)</f>
+        <v>741556488.15382314</v>
       </c>
       <c r="K4" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D11,Rubella!$F$13)</f>
-        <v>1000029267.9655296</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C11,Rubella!$D$2)</f>
+        <v>763885830.22618496</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -3098,44 +3214,44 @@
         <v>7</v>
       </c>
       <c r="B5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D2,Diphtheria!$F$13)</f>
-        <v>1123442883.2120934</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C2,Diphtheria!$D$2)</f>
+        <v>742785491.46924627</v>
       </c>
       <c r="C5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D3,Diphtheria!$F$13)</f>
-        <v>760581543.52950549</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C3,Diphtheria!$D$2)</f>
+        <v>752853587.4273622</v>
       </c>
       <c r="D5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D4,Diphtheria!$F$13)</f>
-        <v>808863065.2732867</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C4,Diphtheria!$D$2)</f>
+        <v>846484448.36472392</v>
       </c>
       <c r="E5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D5,Diphtheria!$F$13)</f>
-        <v>403718480.24675459</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C5,Diphtheria!$D$2)</f>
+        <v>911331567.75979292</v>
       </c>
       <c r="F5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D6,Diphtheria!$F$13)</f>
-        <v>938140151.90137815</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C6,Diphtheria!$D$2)</f>
+        <v>904479481.78190124</v>
       </c>
       <c r="G5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D8,Diphtheria!$F$13)</f>
-        <v>1249538752.1930645</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C8,Diphtheria!$D$2)</f>
+        <v>1164816092.3500228</v>
       </c>
       <c r="H5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D9,Diphtheria!$F$13)</f>
-        <v>936954635.58204234</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C9,Diphtheria!$D$2)</f>
+        <v>1458084052.6528018</v>
       </c>
       <c r="I5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D10,Diphtheria!$F$13)</f>
-        <v>1058037518.6819162</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C10,Diphtheria!$D$2)</f>
+        <v>1527318076.5038919</v>
       </c>
       <c r="J5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D10,Diphtheria!$F$13)</f>
-        <v>1087653563.6034088</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C10,Diphtheria!$D$2)</f>
+        <v>1591242235.5884593</v>
       </c>
       <c r="K5" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D11,Diphtheria!$F$13)</f>
-        <v>1665762716.9262967</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C11,Diphtheria!$D$2)</f>
+        <v>1920616477.7595139</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -3143,44 +3259,44 @@
         <v>8</v>
       </c>
       <c r="B6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D2,Tetanus!$F$13)</f>
-        <v>494157280.53761899</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C2,Tetanus!$D$2)</f>
+        <v>602773484.32235479</v>
       </c>
       <c r="C6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D3,Tetanus!$F$13)</f>
-        <v>537365468.58443594</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C3,Tetanus!$D$2)</f>
+        <v>640837760.7040205</v>
       </c>
       <c r="D6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D4,Tetanus!$F$13)</f>
-        <v>718816673.81974113</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C4,Tetanus!$D$2)</f>
+        <v>685019527.58840501</v>
       </c>
       <c r="E6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D5,Tetanus!$F$13)</f>
-        <v>616884565.48521125</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C5,Tetanus!$D$2)</f>
+        <v>628349818.47549438</v>
       </c>
       <c r="F6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D6,Tetanus!$F$13)</f>
-        <v>743327803.48039961</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C6,Tetanus!$D$2)</f>
+        <v>641662353.09790337</v>
       </c>
       <c r="G6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D7,Tetanus!$F$13)</f>
-        <v>679547072.95331299</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C7,Tetanus!$D$2)</f>
+        <v>679487017.55810404</v>
       </c>
       <c r="H6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D8,Tetanus!$F$13)</f>
-        <v>649080688.50381494</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C8,Tetanus!$D$2)</f>
+        <v>652578957.22678268</v>
       </c>
       <c r="I6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D9,Tetanus!$F$13)</f>
-        <v>621232258.92640686</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C9,Tetanus!$D$2)</f>
+        <v>663703060.87461042</v>
       </c>
       <c r="J6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D10,Tetanus!$F$13)</f>
-        <v>723496931.8686372</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C10,Tetanus!$D$2)</f>
+        <v>691493859.20329762</v>
       </c>
       <c r="K6" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D11,Tetanus!$F$13)</f>
-        <v>510073742.07704681</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C11,Tetanus!$D$2)</f>
+        <v>652692515.10939085</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -3188,44 +3304,44 @@
         <v>9</v>
       </c>
       <c r="B7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D2,Pertussis!$F$13)</f>
-        <v>349521208.98853433</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C2,Pertussis!$D$2)</f>
+        <v>362422627.99443895</v>
       </c>
       <c r="C7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D2,Pertussis!$F$13)</f>
-        <v>431692900.36776066</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C2,Pertussis!$D$2)</f>
+        <v>315701250.17060524</v>
       </c>
       <c r="D7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D4,Pertussis!$F$13)</f>
-        <v>414506121.0054183</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C4,Pertussis!$D$2)</f>
+        <v>368472445.85273087</v>
       </c>
       <c r="E7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D5,Pertussis!$F$13)</f>
-        <v>389086827.05914652</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C5,Pertussis!$D$2)</f>
+        <v>317119649.02451921</v>
       </c>
       <c r="F7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D6,Pertussis!$F$13)</f>
-        <v>328572142.56714904</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C6,Pertussis!$D$2)</f>
+        <v>376239025.84218717</v>
       </c>
       <c r="G7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D7,Pertussis!$F$13)</f>
-        <v>433502559.49073392</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C7,Pertussis!$D$2)</f>
+        <v>374412379.16049558</v>
       </c>
       <c r="H7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D8,Pertussis!$F$13)</f>
-        <v>301740966.09930253</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C8,Pertussis!$D$2)</f>
+        <v>356424154.96221793</v>
       </c>
       <c r="I7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D9,Pertussis!$F$13)</f>
-        <v>315575726.75245166</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C9,Pertussis!$D$2)</f>
+        <v>387528371.29742432</v>
       </c>
       <c r="J7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D10,Pertussis!$F$13)</f>
-        <v>440707781.5308395</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C10,Pertussis!$D$2)</f>
+        <v>357256293.51931</v>
       </c>
       <c r="K7" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D11,Pertussis!$F$13)</f>
-        <v>233020369.69882864</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C11,Pertussis!$D$2)</f>
+        <v>350848044.49634397</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -3233,44 +3349,44 @@
         <v>10</v>
       </c>
       <c r="B8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D2,Hepatitis_B!$F$13)</f>
-        <v>384895186.13944066</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C2,Hepatitis_B!$D$2)</f>
+        <v>395303027.42456394</v>
       </c>
       <c r="C8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D3,Hepatitis_B!$F$13)</f>
-        <v>527370095.49540412</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C3,Hepatitis_B!$D$2)</f>
+        <v>408220393.14708143</v>
       </c>
       <c r="D8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D4,Hepatitis_B!$F$13)</f>
-        <v>580061043.79803181</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C4,Hepatitis_B!$D$2)</f>
+        <v>444641915.07728684</v>
       </c>
       <c r="E8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D5,Hepatitis_B!$F$13)</f>
-        <v>367170060.14926147</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C5,Hepatitis_B!$D$2)</f>
+        <v>453827503.85857785</v>
       </c>
       <c r="F8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D6,Hepatitis_B!$F$13)</f>
-        <v>367887653.91808963</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C6,Hepatitis_B!$D$2)</f>
+        <v>383013545.72927064</v>
       </c>
       <c r="G8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D7,Hepatitis_B!$F$13)</f>
-        <v>315906475.65011495</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C7,Hepatitis_B!$D$2)</f>
+        <v>379502006.21421438</v>
       </c>
       <c r="H8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D8,Hepatitis_B!$F$13)</f>
-        <v>201180556.01515657</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C8,Hepatitis_B!$D$2)</f>
+        <v>401255114.97082168</v>
       </c>
       <c r="I8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D9,Hepatitis_B!$F$13)</f>
-        <v>686135126.50546062</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C9,Hepatitis_B!$D$2)</f>
+        <v>444774444.58579254</v>
       </c>
       <c r="J8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D10,Hepatitis_B!$F$13)</f>
-        <v>403934581.52783585</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C10,Hepatitis_B!$D$2)</f>
+        <v>403463446.28985393</v>
       </c>
       <c r="K8" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D11,Hepatitis_B!$F$13)</f>
-        <v>619312530.39886892</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C11,Hepatitis_B!$D$2)</f>
+        <v>467796355.77015615</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -3278,44 +3394,44 @@
         <v>11</v>
       </c>
       <c r="B9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D2,Hib!$F$13)</f>
-        <v>345360992.16389352</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C2,Hib!$D$2)</f>
+        <v>314257258.63745034</v>
       </c>
       <c r="C9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D3,Hib!$F$13)</f>
-        <v>338107043.03026891</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C3,Hib!$D$2)</f>
+        <v>314152799.93181235</v>
       </c>
       <c r="D9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D4,Hib!$F$13)</f>
-        <v>266697082.57227737</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C4,Hib!$D$2)</f>
+        <v>350041789.64064449</v>
       </c>
       <c r="E9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D5,Hib!$F$13)</f>
-        <v>306958981.54394561</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C5,Hib!$D$2)</f>
+        <v>301268334.68733639</v>
       </c>
       <c r="F9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D6,Hib!$F$13)</f>
-        <v>382015773.38942373</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C6,Hib!$D$2)</f>
+        <v>352128748.55086374</v>
       </c>
       <c r="G9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D7,Hib!$F$13)</f>
-        <v>344414358.96267444</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C7,Hib!$D$2)</f>
+        <v>355668888.58184254</v>
       </c>
       <c r="H9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D8,Hib!$F$13)</f>
-        <v>342642948.07313633</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C8,Hib!$D$2)</f>
+        <v>398675396.96262902</v>
       </c>
       <c r="I9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D9,Hib!$F$13)</f>
-        <v>362039763.82889336</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C9,Hib!$D$2)</f>
+        <v>427391965.79788744</v>
       </c>
       <c r="J9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D10,Hib!$F$13)</f>
-        <v>314379291.95968014</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C10,Hib!$D$2)</f>
+        <v>352020151.85880196</v>
       </c>
       <c r="K9" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D11,Hib!$F$13)</f>
-        <v>447264457.43530977</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C11,Hib!$D$2)</f>
+        <v>434381232.9750579</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -3323,44 +3439,44 @@
         <v>12</v>
       </c>
       <c r="B10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D2,Polio!$F$13)</f>
-        <v>876584392.6378653</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C2,Polio!$D$2)</f>
+        <v>562510067.91676295</v>
       </c>
       <c r="C10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D3,Polio!$F$13)</f>
-        <v>367488774.11160153</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C3,Polio!$D$2)</f>
+        <v>686050307.64316642</v>
       </c>
       <c r="D10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D4,Polio!$F$13)</f>
-        <v>737816468.55611467</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C4,Polio!$D$2)</f>
+        <v>575413534.3232224</v>
       </c>
       <c r="E10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D5,Polio!$F$13)</f>
-        <v>546602869.04926336</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C5,Polio!$D$2)</f>
+        <v>687383594.87407196</v>
       </c>
       <c r="F10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D6,Polio!$F$13)</f>
-        <v>683420219.39665222</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C6,Polio!$D$2)</f>
+        <v>697755472.33727348</v>
       </c>
       <c r="G10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D7,Polio!$F$13)</f>
-        <v>628511301.666255</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C7,Polio!$D$2)</f>
+        <v>780317577.12405515</v>
       </c>
       <c r="H10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D8,Polio!$F$13)</f>
-        <v>941933493.99268901</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C8,Polio!$D$2)</f>
+        <v>749736107.30519927</v>
       </c>
       <c r="I10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D9,Polio!$F$13)</f>
-        <v>970662569.8041985</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C9,Polio!$D$2)</f>
+        <v>870930380.34278071</v>
       </c>
       <c r="J10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D10,Polio!$F$13)</f>
-        <v>882526023.78850722</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C10,Polio!$D$2)</f>
+        <v>907526188.16005743</v>
       </c>
       <c r="K10" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D11,Polio!$F$13)</f>
-        <v>923352564.87766623</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C11,Polio!$D$2)</f>
+        <v>892368067.98188782</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -3368,44 +3484,44 @@
         <v>13</v>
       </c>
       <c r="B11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D2,HPV!$F$13)</f>
-        <v>29217931.001447797</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C2,HPV!$D$2)</f>
+        <v>29375908.204356764</v>
       </c>
       <c r="C11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D3,HPV!$F$13)</f>
-        <v>32173817.862811469</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C3,HPV!$D$2)</f>
+        <v>36973240.974811286</v>
       </c>
       <c r="D11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D4,HPV!$F$13)</f>
-        <v>30549374.685085159</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C4,HPV!$D$2)</f>
+        <v>42810635.44118131</v>
       </c>
       <c r="E11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D5,HPV!$F$13)</f>
-        <v>42905179.298752442</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C5,HPV!$D$2)</f>
+        <v>46450943.908866525</v>
       </c>
       <c r="F11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D6,HPV!$F$13)</f>
-        <v>57101509.13748049</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C6,HPV!$D$2)</f>
+        <v>55751458.96213802</v>
       </c>
       <c r="G11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D7,HPV!$F$13)</f>
-        <v>51936787.984526694</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C7,HPV!$D$2)</f>
+        <v>58567348.47724364</v>
       </c>
       <c r="H11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D8,HPV!$F$13)</f>
-        <v>61497449.02119904</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C8,HPV!$D$2)</f>
+        <v>67149671.127208233</v>
       </c>
       <c r="I11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D9,HPV!$F$13)</f>
-        <v>70092761.038888514</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C9,HPV!$D$2)</f>
+        <v>71955815.934473842</v>
       </c>
       <c r="J11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D10,HPV!$F$13)</f>
-        <v>77539450.587859347</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C10,HPV!$D$2)</f>
+        <v>81054530.296169713</v>
       </c>
       <c r="K11" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D11,HPV!$F$13)</f>
-        <v>89725949.308253497</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C11,HPV!$D$2)</f>
+        <v>89313131.797970936</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -3413,44 +3529,44 @@
         <v>14</v>
       </c>
       <c r="B12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D2,Rotavirus!$F$13)</f>
-        <v>271208223.3028248</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C2,Rotavirus!$D$2)</f>
+        <v>225177168.58647105</v>
       </c>
       <c r="C12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D3,Rotavirus!$F$13)</f>
-        <v>-29820513.577628702</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C3,Rotavirus!$D$2)</f>
+        <v>211818559.40818676</v>
       </c>
       <c r="D12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D4,Rotavirus!$F$13)</f>
-        <v>265335387.09170458</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C4,Rotavirus!$D$2)</f>
+        <v>197255863.65012899</v>
       </c>
       <c r="E12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D5,Rotavirus!$F$13)</f>
-        <v>322737358.79651904</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C5,Rotavirus!$D$2)</f>
+        <v>292473628.34834433</v>
       </c>
       <c r="F12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D6,Rotavirus!$F$13)</f>
-        <v>437375982.26865387</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C6,Rotavirus!$D$2)</f>
+        <v>338275388.45804477</v>
       </c>
       <c r="G12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D7,Rotavirus!$F$13)</f>
-        <v>430995369.69622892</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C7,Rotavirus!$D$2)</f>
+        <v>381248305.86100721</v>
       </c>
       <c r="H12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D8,Rotavirus!$F$13)</f>
-        <v>277857332.80848122</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C8,Rotavirus!$D$2)</f>
+        <v>444205575.87645489</v>
       </c>
       <c r="I12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D9,Rotavirus!$F$13)</f>
-        <v>394733238.23752886</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C9,Rotavirus!$D$2)</f>
+        <v>529896172.87651294</v>
       </c>
       <c r="J12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D10,Rotavirus!$F$13)</f>
-        <v>639274118.27673209</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C10,Rotavirus!$D$2)</f>
+        <v>663705067.16484177</v>
       </c>
       <c r="K12" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D11,Rotavirus!$F$13)</f>
-        <v>722629654.12376082</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C11,Rotavirus!$D$2)</f>
+        <v>735092352.48062396</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -3458,44 +3574,44 @@
         <v>15</v>
       </c>
       <c r="B13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D2,PCV!$F$13)</f>
-        <v>242922527.79350901</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C2,PCV!$D$2)</f>
+        <v>241071149.45158824</v>
       </c>
       <c r="C13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D3,PCV!$F$13)</f>
-        <v>208623178.31365064</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C3,PCV!$D$2)</f>
+        <v>254015380.07613316</v>
       </c>
       <c r="D13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D4,PCV!$F$13)</f>
-        <v>377479630.66208327</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C4,PCV!$D$2)</f>
+        <v>290306034.27144468</v>
       </c>
       <c r="E13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D5,PCV!$F$13)</f>
-        <v>235745910.90144414</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C5,PCV!$D$2)</f>
+        <v>306939644.52600533</v>
       </c>
       <c r="F13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D6,PCV!$F$13)</f>
-        <v>196188626.11846769</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C6,PCV!$D$2)</f>
+        <v>336686422.01807326</v>
       </c>
       <c r="G13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D7,PCV!$F$13)</f>
-        <v>243264208.43181372</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C7,PCV!$D$2)</f>
+        <v>369304271.70029795</v>
       </c>
       <c r="H13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D8,PCV!$F$13)</f>
-        <v>359744862.80326867</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C8,PCV!$D$2)</f>
+        <v>410655800.2244851</v>
       </c>
       <c r="I13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D9,PCV!$F$13)</f>
-        <v>330044939.63516736</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C9,PCV!$D$2)</f>
+        <v>442999496.19893312</v>
       </c>
       <c r="J13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D10,PCV!$F$13)</f>
-        <v>515014051.08443564</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C10,PCV!$D$2)</f>
+        <v>475584022.34082985</v>
       </c>
       <c r="K13" s="4">
-        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D11,PCV!$F$13)</f>
-        <v>340189047.04077357</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C11,PCV!$D$2)</f>
+        <v>454731642.6732856</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -3504,43 +3620,43 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(B2&gt;Measles!B2,Measles!B2,IF(Scenario_data!B2 &lt;Measles!A2,Measles!A2,Scenario_data!B2))</f>
-        <v>247987687.94228613</v>
+        <v>610366749.10346115</v>
       </c>
       <c r="C15" s="7">
         <f ca="1">IF(C2&gt;Measles!B3,Measles!B3,IF(Scenario_data!C2 &lt;Measles!A3,Measles!A3,Scenario_data!C2))</f>
-        <v>510707011.35090262</v>
+        <v>531163244.01083982</v>
       </c>
       <c r="D15" s="7">
         <f ca="1">IF(D2&gt;Measles!B4,Measles!B4,IF(Scenario_data!D2 &lt;Measles!A4,Measles!A4,Scenario_data!D2))</f>
-        <v>779187588.44929445</v>
+        <v>799734080.94260573</v>
       </c>
       <c r="E15" s="7">
         <f ca="1">IF(E2&gt;Measles!B5,Measles!B5,IF(Scenario_data!E2 &lt;Measles!A5,Measles!A5,Scenario_data!E2))</f>
-        <v>856320288.8265897</v>
+        <v>582478519.84207511</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">IF(F2&gt;Measles!B6,Measles!B6,IF(Scenario_data!F2 &lt;Measles!A6,Measles!A6,Scenario_data!F2))</f>
-        <v>609012423.49302292</v>
+        <v>585579461.66020167</v>
       </c>
       <c r="G15" s="7">
         <f ca="1">IF(G2&gt;Measles!B7,Measles!B7,IF(Scenario_data!G2 &lt;Measles!A7,Measles!A7,Scenario_data!G2))</f>
-        <v>1143241091.3296049</v>
+        <v>795043869.14612949</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">IF(H2&gt;Measles!B8,Measles!B8,IF(Scenario_data!H2 &lt;Measles!A8,Measles!A8,Scenario_data!H2))</f>
-        <v>995456032.3599751</v>
+        <v>777274926.59863842</v>
       </c>
       <c r="I15" s="7">
         <f ca="1">IF(I2&gt;Measles!B9,Measles!B9,IF(Scenario_data!I2 &lt;Measles!A9,Measles!A9,Scenario_data!I2))</f>
-        <v>842337190.69581425</v>
+        <v>812112294.92690504</v>
       </c>
       <c r="J15" s="7">
         <f ca="1">IF(J2&gt;Measles!B10,Measles!B10,IF(Scenario_data!J2 &lt;Measles!A10,Measles!A10,Scenario_data!J2))</f>
-        <v>1383348569.0750978</v>
+        <v>916431319.59162045</v>
       </c>
       <c r="K15" s="7">
         <f ca="1">IF(K2&gt;Measles!B11,Measles!B11,IF(Scenario_data!K2 &lt;Measles!A11,Measles!A11,Scenario_data!K2))</f>
-        <v>1017644951.862873</v>
+        <v>788606590.24584341</v>
       </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
@@ -3551,43 +3667,43 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(B3&gt;Mumps!B2,Mumps!B2,IF(Scenario_data!B3 &lt;Mumps!A2,Mumps!A2,Scenario_data!B3))</f>
-        <v>39449727.696229212</v>
+        <v>20151026.863962889</v>
       </c>
       <c r="C16" s="7">
         <f ca="1">IF(C3&gt;Mumps!B3,Mumps!B3,IF(Scenario_data!C3 &lt;Mumps!A3,Mumps!A3,Scenario_data!C3))</f>
-        <v>22092075.843436118</v>
+        <v>25356646.942508951</v>
       </c>
       <c r="D16" s="7">
         <f ca="1">IF(D3&gt;Mumps!B4,Mumps!B4,IF(Scenario_data!D3 &lt;Mumps!A4,Mumps!A4,Scenario_data!D3))</f>
-        <v>14054469.562461421</v>
+        <v>27543029.649350435</v>
       </c>
       <c r="E16" s="7">
         <f ca="1">IF(E3&gt;Mumps!B5,Mumps!B5,IF(Scenario_data!E3 &lt;Mumps!A5,Mumps!A5,Scenario_data!E3))</f>
-        <v>58850113.188332558</v>
+        <v>37009863.591849729</v>
       </c>
       <c r="F16" s="7">
         <f ca="1">IF(F3&gt;Mumps!B6,Mumps!B6,IF(Scenario_data!F3 &lt;Mumps!A6,Mumps!A6,Scenario_data!F3))</f>
-        <v>26097197.900835525</v>
+        <v>36017326.664739236</v>
       </c>
       <c r="G16" s="7">
         <f ca="1">IF(G3&gt;Mumps!B7,Mumps!B7,IF(Scenario_data!G3 &lt;Mumps!A7,Mumps!A7,Scenario_data!G3))</f>
-        <v>34164435.01032491</v>
+        <v>41641280.211628623</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">IF(H3&gt;Mumps!B8,Mumps!B8,IF(Scenario_data!H3 &lt;Mumps!A8,Mumps!A8,Scenario_data!H3))</f>
-        <v>85093245.656676412</v>
+        <v>38600796.984534249</v>
       </c>
       <c r="I16" s="7">
         <f ca="1">IF(I3&gt;Mumps!B9,Mumps!B9,IF(Scenario_data!I3 &lt;Mumps!A9,Mumps!A9,Scenario_data!I3))</f>
-        <v>28777382.649661399</v>
+        <v>46346411.309301585</v>
       </c>
       <c r="J16" s="7">
         <f ca="1">IF(J3&gt;Mumps!B10,Mumps!B10,IF(Scenario_data!J3 &lt;Mumps!A10,Mumps!A10,Scenario_data!J3))</f>
-        <v>20864361.672251873</v>
+        <v>52122361.570719413</v>
       </c>
       <c r="K16" s="7">
         <f ca="1">IF(K3&gt;Mumps!B11,Mumps!B11,IF(Scenario_data!K3 &lt;Mumps!A11,Mumps!A11,Scenario_data!K3))</f>
-        <v>70486241.419496059</v>
+        <v>63584922.777330749</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -3596,43 +3712,43 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(B4&gt;Rubella!B2,Rubella!B2,IF(Scenario_data!B4 &lt;Rubella!A2,Rubella!A2,Scenario_data!B4))</f>
-        <v>190948844.07116279</v>
+        <v>269979741.65914881</v>
       </c>
       <c r="C17" s="7">
         <f ca="1">IF(C4&gt;Rubella!B3,Rubella!B3,IF(Scenario_data!C4 &lt;Rubella!A3,Rubella!A3,Scenario_data!C4))</f>
-        <v>267844914.35984373</v>
+        <v>424620184.82685202</v>
       </c>
       <c r="D17" s="7">
         <f ca="1">IF(D4&gt;Rubella!B4,Rubella!B4,IF(Scenario_data!D4 &lt;Rubella!A4,Rubella!A4,Scenario_data!D4))</f>
-        <v>197265695.85591027</v>
+        <v>458445881.5196749</v>
       </c>
       <c r="E17" s="7">
         <f ca="1">IF(E4&gt;Rubella!B5,Rubella!B5,IF(Scenario_data!E4 &lt;Rubella!A5,Rubella!A5,Scenario_data!E4))</f>
-        <v>689555343.34359598</v>
+        <v>441303051.16330719</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">IF(F4&gt;Rubella!B6,Rubella!B6,IF(Scenario_data!F4 &lt;Rubella!A6,Rubella!A6,Scenario_data!F4))</f>
-        <v>935183993.09773898</v>
+        <v>518738648.8944546</v>
       </c>
       <c r="G17" s="7">
         <f ca="1">IF(G4&gt;Rubella!B7,Rubella!B7,IF(Scenario_data!G4 &lt;Rubella!A7,Rubella!A7,Scenario_data!G4))</f>
-        <v>825663716.02607489</v>
+        <v>560590321.12412798</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">IF(H4&gt;Rubella!B8,Rubella!B8,IF(Scenario_data!H4 &lt;Rubella!A8,Rubella!A8,Scenario_data!H4))</f>
-        <v>476314964.47713357</v>
+        <v>619263506.51350164</v>
       </c>
       <c r="I17" s="7">
         <f ca="1">IF(I4&gt;Rubella!B9,Rubella!B9,IF(Scenario_data!I4 &lt;Rubella!A9,Rubella!A9,Scenario_data!I4))</f>
-        <v>288335650.59274518</v>
+        <v>597953201.04888475</v>
       </c>
       <c r="J17" s="7">
         <f ca="1">IF(J4&gt;Rubella!B10,Rubella!B10,IF(Scenario_data!J4 &lt;Rubella!A10,Rubella!A10,Scenario_data!J4))</f>
-        <v>783705380.60791039</v>
+        <v>741556488.15382314</v>
       </c>
       <c r="K17" s="7">
         <f ca="1">IF(K4&gt;Rubella!B12=1,Rubella!B11,IF(Scenario_data!K4 &lt;Rubella!A11,Rubella!A11,Scenario_data!K4))</f>
-        <v>1000029267.9655296</v>
+        <v>763885830.22618496</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -3641,43 +3757,43 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(B5&gt;Diphtheria!B2,Diphtheria!B2,IF(Scenario_data!B5 &lt;Diphtheria!A2,Diphtheria!A2,Scenario_data!B5))</f>
-        <v>777076702.64843607</v>
+        <v>742785491.46924627</v>
       </c>
       <c r="C18" s="7">
         <f ca="1">IF(C5&gt;Diphtheria!B3,Diphtheria!B3,IF(Scenario_data!C5 &lt;Diphtheria!A3,Diphtheria!A3,Scenario_data!C5))</f>
-        <v>760581543.52950549</v>
+        <v>752853587.4273622</v>
       </c>
       <c r="D18" s="7">
         <f ca="1">IF(D5&gt;Diphtheria!B4,Diphtheria!B4,IF(Scenario_data!D5 &lt;Diphtheria!A4,Diphtheria!A4,Scenario_data!D5))</f>
-        <v>808863065.2732867</v>
+        <v>846484448.36472392</v>
       </c>
       <c r="E18" s="7">
         <f ca="1">IF(E5&gt;Diphtheria!B5,Diphtheria!B5,IF(Scenario_data!E5 &lt;Diphtheria!A5,Diphtheria!A5,Scenario_data!E5))</f>
-        <v>437709524.92591959</v>
+        <v>911331567.75979292</v>
       </c>
       <c r="F18" s="7">
         <f ca="1">IF(F5&gt;Diphtheria!B6,Diphtheria!B6,IF(Scenario_data!F5 &lt;Diphtheria!A6,Diphtheria!A6,Scenario_data!F5))</f>
-        <v>938140151.90137815</v>
+        <v>904479481.78190124</v>
       </c>
       <c r="G18" s="7">
         <f ca="1">IF(G5&gt;Diphtheria!B7,Diphtheria!B7,IF(Scenario_data!G5 &lt;Diphtheria!A7,Diphtheria!A7,Scenario_data!G5))</f>
-        <v>1249538752.1930645</v>
+        <v>1164816092.3500228</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">IF(H5&gt;Diphtheria!B8,Diphtheria!B8,IF(Scenario_data!H5 &lt;Diphtheria!A8,Diphtheria!A8,Scenario_data!H5))</f>
-        <v>936954635.58204234</v>
+        <v>1458084052.6528018</v>
       </c>
       <c r="I18" s="7">
         <f ca="1">IF(I5&gt;Diphtheria!B9,Diphtheria!B9,IF(Scenario_data!I5 &lt;Diphtheria!A9,Diphtheria!A9,Scenario_data!I5))</f>
-        <v>1058037518.6819162</v>
+        <v>1527318076.5038919</v>
       </c>
       <c r="J18" s="7">
         <f ca="1">IF(J5&gt;Diphtheria!B10,Diphtheria!B10,IF(Scenario_data!J5 &lt;Diphtheria!A10,Diphtheria!A10,Scenario_data!J5))</f>
-        <v>1087653563.6034088</v>
+        <v>1591242235.5884593</v>
       </c>
       <c r="K18" s="7">
         <f ca="1">IF(K5&gt;Diphtheria!B11,Diphtheria!B11,IF(Scenario_data!K5 &lt;Diphtheria!A11,Diphtheria!A11,Scenario_data!K5))</f>
-        <v>1665762716.9262967</v>
+        <v>1920616477.7595139</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -3686,43 +3802,43 @@
       </c>
       <c r="B19" s="7">
         <f ca="1">IF(B6&gt;Tetanus!B2,Tetanus!B2,IF(Scenario_data!B6 &lt;Tetanus!A2,Tetanus!A2,Scenario_data!B6))</f>
-        <v>570605073.91759527</v>
+        <v>602773484.32235479</v>
       </c>
       <c r="C19" s="7">
         <f ca="1">IF(C6&gt;Tetanus!B3,Tetanus!B3,IF(Scenario_data!C6 &lt;Tetanus!A3,Tetanus!A3,Scenario_data!C6))</f>
-        <v>546556435.55415082</v>
+        <v>640837760.7040205</v>
       </c>
       <c r="D19" s="7">
         <f ca="1">IF(D6&gt;Tetanus!B4,Tetanus!B4,IF(Scenario_data!D6 &lt;Tetanus!A4,Tetanus!A4,Scenario_data!D6))</f>
-        <v>718816673.81974113</v>
+        <v>685019527.58840501</v>
       </c>
       <c r="E19" s="7">
         <f ca="1">IF(E6&gt;Tetanus!B5,Tetanus!B5,IF(Scenario_data!E6 &lt;Tetanus!A5,Tetanus!A5,Scenario_data!E6))</f>
-        <v>616884565.48521125</v>
+        <v>628349818.47549438</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">IF(F6&gt;Tetanus!B6,Tetanus!B6,IF(Scenario_data!F6 &lt;Tetanus!A6,Tetanus!A6,Scenario_data!F6))</f>
-        <v>743327803.48039961</v>
+        <v>641662353.09790337</v>
       </c>
       <c r="G19" s="7">
         <f ca="1">IF(G6&gt;Tetanus!B7,Tetanus!B7,IF(Scenario_data!G6 &lt;Tetanus!A7,Tetanus!A7,Scenario_data!G6))</f>
-        <v>679547072.95331299</v>
+        <v>679487017.55810404</v>
       </c>
       <c r="H19" s="7">
         <f ca="1">IF(H6&gt;Tetanus!B8,Tetanus!B8,IF(Scenario_data!H6 &lt;Tetanus!A8,Tetanus!A8,Scenario_data!H6))</f>
-        <v>649080688.50381494</v>
+        <v>652578957.22678268</v>
       </c>
       <c r="I19" s="7">
         <f ca="1">IF(I6&gt;Tetanus!B9,Tetanus!B9,IF(Scenario_data!I6 &lt;Tetanus!A9,Tetanus!A9,Scenario_data!I6))</f>
-        <v>621232258.92640686</v>
+        <v>663703060.87461042</v>
       </c>
       <c r="J19" s="7">
         <f ca="1">IF(J6&gt;Tetanus!B10,Tetanus!B10,IF(Scenario_data!J6 &lt;Tetanus!A10,Tetanus!A10,Scenario_data!J6))</f>
-        <v>723496931.8686372</v>
+        <v>691493859.20329762</v>
       </c>
       <c r="K19" s="7">
         <f ca="1">IF(K6&gt;Tetanus!B11,Tetanus!B11,IF(Scenario_data!K6 &lt;Tetanus!A11,Tetanus!A11,Scenario_data!K6))</f>
-        <v>510073742.07704681</v>
+        <v>652692515.10939085</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -3731,43 +3847,43 @@
       </c>
       <c r="B20" s="7">
         <f ca="1">IF(B7&gt;Pertussis!B2,Pertussis!B2,IF(Scenario_data!B7 &lt;Pertussis!A2,Pertussis!A2,Scenario_data!B7))</f>
-        <v>349521208.98853433</v>
+        <v>362422627.99443895</v>
       </c>
       <c r="C20" s="7">
         <f ca="1">IF(C7&gt;Pertussis!B3,Pertussis!B3,IF(Scenario_data!C7 &lt;Pertussis!A3,Pertussis!A3,Scenario_data!C7))</f>
-        <v>418726778.96281028</v>
+        <v>315701250.17060524</v>
       </c>
       <c r="D20" s="7">
         <f ca="1">IF(D7&gt;Pertussis!B4,Pertussis!B4,IF(Scenario_data!D7 &lt;Pertussis!A4,Pertussis!A4,Scenario_data!D7))</f>
-        <v>414506121.0054183</v>
+        <v>368472445.85273087</v>
       </c>
       <c r="E20" s="7">
         <f ca="1">IF(E7&gt;Pertussis!B5,Pertussis!B5,IF(Scenario_data!E7 &lt;Pertussis!A5,Pertussis!A5,Scenario_data!E7))</f>
-        <v>389086827.05914652</v>
+        <v>317119649.02451921</v>
       </c>
       <c r="F20" s="7">
         <f ca="1">IF(F7&gt;Pertussis!B6,Pertussis!B6,IF(Scenario_data!F7 &lt;Pertussis!A6,Pertussis!A6,Scenario_data!F7))</f>
-        <v>328572142.56714904</v>
+        <v>376239025.84218717</v>
       </c>
       <c r="G20" s="7">
         <f ca="1">IF(G7&gt;Pertussis!B7,Pertussis!B7,IF(Scenario_data!G7 &lt;Pertussis!A7,Pertussis!A7,Scenario_data!G7))</f>
-        <v>433502559.49073392</v>
+        <v>374412379.16049558</v>
       </c>
       <c r="H20" s="7">
         <f ca="1">IF(H7&gt;Pertussis!B8,Pertussis!B8,IF(Scenario_data!H7 &lt;Pertussis!A8,Pertussis!A8,Scenario_data!H7))</f>
-        <v>301740966.09930253</v>
+        <v>356424154.96221793</v>
       </c>
       <c r="I20" s="7">
         <f ca="1">IF(I7&gt;Pertussis!B9,Pertussis!B9,IF(Scenario_data!I7 &lt;Pertussis!A9,Pertussis!A9,Scenario_data!I7))</f>
-        <v>315575726.75245166</v>
+        <v>387528371.29742432</v>
       </c>
       <c r="J20" s="7">
         <f ca="1">IF(J7&gt;Pertussis!B10,Pertussis!B10,IF(Scenario_data!J7 &lt;Pertussis!A10,Pertussis!A10,Scenario_data!J7))</f>
-        <v>440707781.5308395</v>
+        <v>357256293.51931</v>
       </c>
       <c r="K20" s="7">
         <f ca="1">IF(K7&gt;Pertussis!B11,Pertussis!B11,IF(Scenario_data!K7 &lt;Pertussis!A11,Pertussis!A11,Scenario_data!K7))</f>
-        <v>233020369.69882864</v>
+        <v>350848044.49634397</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -3776,43 +3892,43 @@
       </c>
       <c r="B21" s="7">
         <f ca="1">IF(B8&gt;Hepatitis_B!B2,Hepatitis_B!B2,IF(Scenario_data!B8 &lt;Hepatitis_B!A2,Hepatitis_B!A2,Scenario_data!B8))</f>
-        <v>384895186.13944066</v>
+        <v>395303027.42456394</v>
       </c>
       <c r="C21" s="7">
         <f ca="1">IF(C8&gt;Hepatitis_B!B3,Hepatitis_B!B3,IF(Scenario_data!C8 &lt;Hepatitis_B!A3,Hepatitis_B!A3,Scenario_data!C8))</f>
-        <v>494109545.4175849</v>
+        <v>408220393.14708143</v>
       </c>
       <c r="D21" s="7">
         <f ca="1">IF(D8&gt;Hepatitis_B!B4,Hepatitis_B!B4,IF(Scenario_data!D8 &lt;Hepatitis_B!A4,Hepatitis_B!A4,Scenario_data!D8))</f>
-        <v>551227913.124102</v>
+        <v>444641915.07728684</v>
       </c>
       <c r="E21" s="7">
         <f ca="1">IF(E8&gt;Hepatitis_B!B5,Hepatitis_B!B5,IF(Scenario_data!E8 &lt;Hepatitis_B!A5,Hepatitis_B!A5,Scenario_data!E8))</f>
-        <v>367170060.14926147</v>
+        <v>453827503.85857785</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">IF(F8&gt;Hepatitis_B!B6,Hepatitis_B!B6,IF(Scenario_data!F8 &lt;Hepatitis_B!A6,Hepatitis_B!A6,Scenario_data!F8))</f>
-        <v>367887653.91808963</v>
+        <v>383013545.72927064</v>
       </c>
       <c r="G21" s="7">
         <f ca="1">IF(G8&gt;Hepatitis_B!B7,Hepatitis_B!B7,IF(Scenario_data!G8 &lt;Hepatitis_B!A7,Hepatitis_B!A7,Scenario_data!G8))</f>
-        <v>315906475.65011495</v>
+        <v>379502006.21421438</v>
       </c>
       <c r="H21" s="7">
         <f ca="1">IF(H8&gt;Hepatitis_B!B8,Hepatitis_B!B8,IF(Scenario_data!H8 &lt;Hepatitis_B!A8,Hepatitis_B!A8,Scenario_data!H8))</f>
-        <v>201180556.01515657</v>
+        <v>401255114.97082168</v>
       </c>
       <c r="I21" s="7">
         <f ca="1">IF(I8&gt;Hepatitis_B!B9,Hepatitis_B!B9,IF(Scenario_data!I8 &lt;Hepatitis_B!A9,Hepatitis_B!A9,Scenario_data!I8))</f>
-        <v>686135126.50546062</v>
+        <v>444774444.58579254</v>
       </c>
       <c r="J21" s="7">
         <f ca="1">IF(J8&gt;Hepatitis_B!B10,Hepatitis_B!B10,IF(Scenario_data!J8 &lt;Hepatitis_B!A10,Hepatitis_B!A10,Scenario_data!J8))</f>
-        <v>403934581.52783585</v>
+        <v>403463446.28985393</v>
       </c>
       <c r="K21" s="7">
         <f ca="1">IF(K8&gt;Hepatitis_B!B11,Hepatitis_B!B11,IF(Scenario_data!K8 &lt;Hepatitis_B!A11,Hepatitis_B!A11,Scenario_data!K8))</f>
-        <v>619312530.39886892</v>
+        <v>467796355.77015615</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -3821,43 +3937,43 @@
       </c>
       <c r="B22" s="7">
         <f ca="1">IF(B9&gt;Hib!B2,Hib!B2,IF(Scenario_data!B9 &lt;Hib!A2,Hib!A2,Scenario_data!B9))</f>
-        <v>335380421.76351452</v>
+        <v>314257258.63745034</v>
       </c>
       <c r="C22" s="7">
         <f ca="1">IF(C9&gt;Hib!B3,Hib!B3,IF(Scenario_data!C9 &lt;Hib!A3,Hib!A3,Scenario_data!C9))</f>
-        <v>338107043.03026891</v>
+        <v>314152799.93181235</v>
       </c>
       <c r="D22" s="7">
         <f ca="1">IF(D9&gt;Hib!B4,Hib!B4,IF(Scenario_data!D9 &lt;Hib!A4,Hib!A4,Scenario_data!D9))</f>
-        <v>266697082.57227737</v>
+        <v>350041789.64064449</v>
       </c>
       <c r="E22" s="7">
         <f ca="1">IF(E9&gt;Hib!B5,Hib!B5,IF(Scenario_data!E9 &lt;Hib!A5,Hib!A5,Scenario_data!E9))</f>
-        <v>306958981.54394561</v>
+        <v>301268334.68733639</v>
       </c>
       <c r="F22" s="7">
         <f ca="1">IF(F9&gt;Hib!B6,Hib!B6,IF(Scenario_data!F9 &lt;Hib!A6,Hib!A6,Scenario_data!F9))</f>
-        <v>382015773.38942373</v>
+        <v>352128748.55086374</v>
       </c>
       <c r="G22" s="7">
         <f ca="1">IF(G9&gt;Hib!B7,Hib!B7,IF(Scenario_data!G9 &lt;Hib!A7,Hib!A7,Scenario_data!G9))</f>
-        <v>344414358.96267444</v>
+        <v>355668888.58184254</v>
       </c>
       <c r="H22" s="7">
         <f ca="1">IF(H9&gt;Hib!B8,Hib!B8,IF(Scenario_data!H9 &lt;Hib!A8,Hib!A8,Scenario_data!H9))</f>
-        <v>342642948.07313633</v>
+        <v>398675396.96262902</v>
       </c>
       <c r="I22" s="7">
         <f ca="1">IF(I9&gt;Hib!B9,Hib!B9,IF(Scenario_data!I9 &lt;Hib!A9,Hib!A9,Scenario_data!I9))</f>
-        <v>362039763.82889336</v>
+        <v>427391965.79788744</v>
       </c>
       <c r="J22" s="7">
         <f ca="1">IF(J9&gt;Hib!B10,Hib!B10,IF(Scenario_data!J9 &lt;Hib!A10,Hib!A10,Scenario_data!J9))</f>
-        <v>314379291.95968014</v>
+        <v>352020151.85880196</v>
       </c>
       <c r="K22" s="7">
         <f ca="1">IF(K9&gt;Hib!B11,Hib!B11,IF(Scenario_data!K9 &lt;Hib!A11,Hib!A11,Scenario_data!K9))</f>
-        <v>447264457.43530977</v>
+        <v>434381232.9750579</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -3866,43 +3982,43 @@
       </c>
       <c r="B23" s="7">
         <f ca="1">IF(B10&gt;Polio!B2,Polio!B2,IF(Scenario_data!B10 &lt;Polio!A2,Polio!A2,Scenario_data!B10))</f>
-        <v>716469135.2208643</v>
+        <v>562510067.91676295</v>
       </c>
       <c r="C23" s="7">
         <f ca="1">IF(C10&gt;Polio!B3,Polio!B3,IF(Scenario_data!C10 &lt;Polio!A3,Polio!A3,Scenario_data!C10))</f>
-        <v>534554254.60230482</v>
+        <v>686050307.64316642</v>
       </c>
       <c r="D23" s="7">
         <f ca="1">IF(D10&gt;Polio!B4,Polio!B4,IF(Scenario_data!D10 &lt;Polio!A4,Polio!A4,Scenario_data!D10))</f>
-        <v>737816468.55611467</v>
+        <v>575413534.3232224</v>
       </c>
       <c r="E23" s="7">
         <f ca="1">IF(E10&gt;Polio!B5,Polio!B5,IF(Scenario_data!E10 &lt;Polio!A5,Polio!A5,Scenario_data!E10))</f>
-        <v>546602869.04926336</v>
+        <v>687383594.87407196</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">IF(F10&gt;Polio!B6,Polio!B6,IF(Scenario_data!F10 &lt;Polio!A6,Polio!A6,Scenario_data!F10))</f>
-        <v>683420219.39665222</v>
+        <v>697755472.33727348</v>
       </c>
       <c r="G23" s="7">
         <f ca="1">IF(G10&gt;Polio!B7,Polio!B7,IF(Scenario_data!G10 &lt;Polio!A7,Polio!A7,Scenario_data!G10))</f>
-        <v>628511301.666255</v>
+        <v>780317577.12405515</v>
       </c>
       <c r="H23" s="7">
         <f ca="1">IF(H10&gt;Polio!B8,Polio!B8,IF(Scenario_data!H10 &lt;Polio!A8,Polio!A8,Scenario_data!H10))</f>
-        <v>941933493.99268901</v>
+        <v>749736107.30519927</v>
       </c>
       <c r="I23" s="7">
         <f ca="1">IF(I10&gt;Polio!B9,Polio!B9,IF(Scenario_data!I10 &lt;Polio!A9,Polio!A9,Scenario_data!I10))</f>
-        <v>970662569.8041985</v>
+        <v>870930380.34278071</v>
       </c>
       <c r="J23" s="7">
         <f ca="1">IF(J10&gt;Polio!B10,Polio!B10,IF(Scenario_data!J10 &lt;Polio!A10,Polio!A10,Scenario_data!J10))</f>
-        <v>882526023.78850722</v>
+        <v>907526188.16005743</v>
       </c>
       <c r="K23" s="7">
         <f ca="1">IF(K10&gt;Polio!B11,Polio!B11,IF(Scenario_data!K10 &lt;Polio!A11,Polio!A11,Scenario_data!K10))</f>
-        <v>923352564.87766623</v>
+        <v>892368067.98188782</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -3911,43 +4027,43 @@
       </c>
       <c r="B24" s="7">
         <f ca="1">IF(B11&gt;HPV!B2,HPV!B2,IF(Scenario_data!B11 &lt;HPV!A2,HPV!A2,Scenario_data!B11))</f>
-        <v>29217931.001447797</v>
+        <v>29375908.204356764</v>
       </c>
       <c r="C24" s="7">
         <f ca="1">IF(C11&gt;HPV!B3,HPV!B3,IF(Scenario_data!C11 &lt;HPV!A3,HPV!A3,Scenario_data!C11))</f>
-        <v>32672389.333723851</v>
+        <v>36973240.974811286</v>
       </c>
       <c r="D24" s="7">
         <f ca="1">IF(D11&gt;HPV!B4,HPV!B4,IF(Scenario_data!D11 &lt;HPV!A4,HPV!A4,Scenario_data!D11))</f>
-        <v>35258738.193920977</v>
+        <v>42810635.44118131</v>
       </c>
       <c r="E24" s="7">
         <f ca="1">IF(E11&gt;HPV!B5,HPV!B5,IF(Scenario_data!E11 &lt;HPV!A5,HPV!A5,Scenario_data!E11))</f>
-        <v>42905179.298752442</v>
+        <v>46450943.908866525</v>
       </c>
       <c r="F24" s="7">
         <f ca="1">IF(F11&gt;HPV!B6,HPV!B6,IF(Scenario_data!F11 &lt;HPV!A6,HPV!A6,Scenario_data!F11))</f>
-        <v>57101509.13748049</v>
+        <v>55751458.96213802</v>
       </c>
       <c r="G24" s="7">
         <f ca="1">IF(G11&gt;HPV!B7,HPV!B7,IF(Scenario_data!G11 &lt;HPV!A7,HPV!A7,Scenario_data!G11))</f>
-        <v>51936787.984526694</v>
+        <v>58567348.47724364</v>
       </c>
       <c r="H24" s="7">
         <f ca="1">IF(H11&gt;HPV!B8,HPV!B8,IF(Scenario_data!H11 &lt;HPV!A8,HPV!A8,Scenario_data!H11))</f>
-        <v>61497449.02119904</v>
+        <v>67149671.127208233</v>
       </c>
       <c r="I24" s="7">
         <f ca="1">IF(I11&gt;HPV!B9,HPV!B9,IF(Scenario_data!I11 &lt;HPV!A9,HPV!A9,Scenario_data!I11))</f>
-        <v>70092761.038888514</v>
+        <v>71955815.934473842</v>
       </c>
       <c r="J24" s="7">
         <f ca="1">IF(J11&gt;HPV!B10,HPV!B10,IF(Scenario_data!J11 &lt;HPV!A10,HPV!A10,Scenario_data!J11))</f>
-        <v>77539450.587859347</v>
+        <v>81054530.296169713</v>
       </c>
       <c r="K24" s="7">
         <f ca="1">IF(K11&gt;HPV!B11,HPV!B11,IF(Scenario_data!K11 &lt;HPV!A11,HPV!A11,Scenario_data!K11))</f>
-        <v>89725949.308253497</v>
+        <v>89313131.797970936</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -3956,43 +4072,43 @@
       </c>
       <c r="B25" s="7">
         <f ca="1">IF(B12&gt;Rotavirus!B2,Rotavirus!B2,IF(Scenario_data!B12 &lt;Rotavirus!A2,Rotavirus!A2,Scenario_data!B12))</f>
-        <v>239577204.00124341</v>
+        <v>225177168.58647105</v>
       </c>
       <c r="C25" s="7">
         <f ca="1">IF(C12&gt;Rotavirus!B3,Rotavirus!B3,IF(Scenario_data!C12 &lt;Rotavirus!A3,Rotavirus!A3,Scenario_data!C12))</f>
-        <v>136461943.51271439</v>
+        <v>211818559.40818676</v>
       </c>
       <c r="D25" s="7">
         <f ca="1">IF(D12&gt;Rotavirus!B4,Rotavirus!B4,IF(Scenario_data!D12 &lt;Rotavirus!A4,Rotavirus!A4,Scenario_data!D12))</f>
-        <v>265335387.09170458</v>
+        <v>197255863.65012899</v>
       </c>
       <c r="E25" s="7">
         <f ca="1">IF(E12&gt;Rotavirus!B5,Rotavirus!B5,IF(Scenario_data!E12 &lt;Rotavirus!A5,Rotavirus!A5,Scenario_data!E12))</f>
-        <v>322737358.79651904</v>
+        <v>292473628.34834433</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">IF(F12&gt;Rotavirus!B6,Rotavirus!B6,IF(Scenario_data!F12 &lt;Rotavirus!A6,Rotavirus!A6,Scenario_data!F12))</f>
-        <v>437375982.26865387</v>
+        <v>338275388.45804477</v>
       </c>
       <c r="G25" s="7">
         <f ca="1">IF(G12&gt;Rotavirus!B7,Rotavirus!B7,IF(Scenario_data!G12 &lt;Rotavirus!A7,Rotavirus!A7,Scenario_data!G12))</f>
-        <v>430995369.69622892</v>
+        <v>381248305.86100721</v>
       </c>
       <c r="H25" s="7">
         <f ca="1">IF(H12&gt;Rotavirus!B8,Rotavirus!B8,IF(Scenario_data!H12 &lt;Rotavirus!A8,Rotavirus!A8,Scenario_data!H12))</f>
-        <v>277857332.80848122</v>
+        <v>444205575.87645489</v>
       </c>
       <c r="I25" s="7">
         <f ca="1">IF(I12&gt;Rotavirus!B9,Rotavirus!B9,IF(Scenario_data!I12 &lt;Rotavirus!A9,Rotavirus!A9,Scenario_data!I12))</f>
-        <v>394733238.23752886</v>
+        <v>529896172.87651294</v>
       </c>
       <c r="J25" s="7">
         <f ca="1">IF(J12&gt;Rotavirus!B10,Rotavirus!B10,IF(Scenario_data!J12 &lt;Rotavirus!A10,Rotavirus!A10,Scenario_data!J12))</f>
-        <v>639274118.27673209</v>
+        <v>663705067.16484177</v>
       </c>
       <c r="K25" s="7">
         <f ca="1">IF(K12&gt;Rotavirus!B11,Rotavirus!B11,IF(Scenario_data!K12 &lt;Rotavirus!A11,Rotavirus!A11,Scenario_data!K12))</f>
-        <v>722629654.12376082</v>
+        <v>735092352.48062396</v>
       </c>
       <c r="M25" s="4"/>
     </row>
@@ -4002,43 +4118,43 @@
       </c>
       <c r="B26" s="7">
         <f ca="1">IF(B13&gt;PCV!B2,PCV!B2,IF(Scenario_data!B13 &lt;PCV!A2,PCV!A2,Scenario_data!B13))</f>
-        <v>242922527.79350901</v>
+        <v>241071149.45158824</v>
       </c>
       <c r="C26" s="7">
         <f ca="1">IF(C13&gt;PCV!B3,PCV!B3,IF(Scenario_data!C13 &lt;PCV!A3,PCV!A3,Scenario_data!C13))</f>
-        <v>208856647.25570789</v>
+        <v>254015380.07613316</v>
       </c>
       <c r="D26" s="7">
         <f ca="1">IF(D13&gt;PCV!B4,PCV!B4,IF(Scenario_data!D13 &lt;PCV!A4,PCV!A4,Scenario_data!D13))</f>
-        <v>363423456.81929737</v>
+        <v>290306034.27144468</v>
       </c>
       <c r="E26" s="7">
         <f ca="1">IF(E13&gt;PCV!B5,PCV!B5,IF(Scenario_data!E13 &lt;PCV!A5,PCV!A5,Scenario_data!E13))</f>
-        <v>235745910.90144414</v>
+        <v>306939644.52600533</v>
       </c>
       <c r="F26" s="7">
         <f ca="1">IF(F13&gt;PCV!B6,PCV!B6,IF(Scenario_data!F13 &lt;PCV!A6,PCV!A6,Scenario_data!F13))</f>
-        <v>196188626.11846769</v>
+        <v>336686422.01807326</v>
       </c>
       <c r="G26" s="7">
         <f ca="1">IF(G13&gt;PCV!B7,PCV!B7,IF(Scenario_data!G13 &lt;PCV!A7,PCV!A7,Scenario_data!G13))</f>
-        <v>243264208.43181372</v>
+        <v>369304271.70029795</v>
       </c>
       <c r="H26" s="7">
         <f ca="1">IF(H13&gt;PCV!B8,PCV!B8,IF(Scenario_data!H13 &lt;PCV!A8,PCV!A8,Scenario_data!H13))</f>
-        <v>359744862.80326867</v>
+        <v>410655800.2244851</v>
       </c>
       <c r="I26" s="7">
         <f ca="1">IF(I13&gt;PCV!B9,PCV!B9,IF(Scenario_data!I13 &lt;PCV!A9,PCV!A9,Scenario_data!I13))</f>
-        <v>330044939.63516736</v>
+        <v>442999496.19893312</v>
       </c>
       <c r="J26" s="7">
         <f ca="1">IF(J13&gt;PCV!B10,PCV!B10,IF(Scenario_data!J13 &lt;PCV!A10,PCV!A10,Scenario_data!J13))</f>
-        <v>515014051.08443564</v>
+        <v>475584022.34082985</v>
       </c>
       <c r="K26" s="7">
         <f ca="1">IF(K13&gt;PCV!B11,PCV!B11,IF(Scenario_data!K13 &lt;PCV!A11,PCV!A11,Scenario_data!K13))</f>
-        <v>340189047.04077357</v>
+        <v>454731642.6732856</v>
       </c>
       <c r="M26" s="4"/>
     </row>
@@ -4223,161 +4339,187 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>313184875.6168254</v>
       </c>
       <c r="B2">
         <v>397026393.63704878</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>355105634.62693709</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>21388142.352097802</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>297220409.07591468</v>
       </c>
       <c r="B3">
         <v>418726778.96281028</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>357973594.01936245</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>30996522.930330526</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>284867436.90863109</v>
       </c>
       <c r="B4">
         <v>437276119.25633711</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>361071778.08248413</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>38879765.905027032</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>274333558.66616201</v>
       </c>
       <c r="B5">
         <v>454473782.72728658</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>364403670.6967243</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>45954138.791103207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>264944390.69536629</v>
       </c>
       <c r="B6">
         <v>471001453.41055518</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>367972922.05296075</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>52565577.223262466</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>256363314.1406557</v>
       </c>
       <c r="B7">
         <v>487203392.12997788</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>371783353.13531679</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>58887774.997276068</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>248395387.0916445</v>
       </c>
       <c r="B8">
         <v>503282533.62184912</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>375838960.35674679</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>65022231.257705271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>240916564.79568711</v>
       </c>
       <c r="B9">
         <v>519371275.90998042</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>380143920.35283375</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>71034365.080176875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>233842532.2153208</v>
       </c>
       <c r="B10">
         <v>535562657.66348678</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>384702594.93940377</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>76969419.757185206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>227113082.79582271</v>
       </c>
       <c r="B11">
         <v>551925989.68367708</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>389519536.23974991</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>264118155.20020303</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>477585037.70030087</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>82860435.430575088</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>370851596.45025194</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>54455837.372473948</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4386,161 +4528,187 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>549827474.98132467</v>
       </c>
       <c r="B2">
         <v>716469135.2208643</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>633148305.10109448</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>42510627.612127453</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>534554254.60230482</v>
       </c>
       <c r="B3">
         <v>783694552.35479057</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>659124403.47854769</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>63556198.406246364</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>525451510.27095741</v>
       </c>
       <c r="B4">
         <v>847853208.89578772</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>686652359.58337259</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>82245331.281844452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>519253104.41226047</v>
       </c>
       <c r="B5">
         <v>912407624.0362891</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>715830364.22427475</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>100294520.31225222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>514757852.06144291</v>
       </c>
       <c r="B6">
         <v>978767909.04237306</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>746762880.55190802</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>118369912.49513523</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>511378303.13956457</v>
       </c>
       <c r="B7">
         <v>1047743797.031805</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>779561050.08568478</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>136827932.11536747</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>508780839.08917749</v>
       </c>
       <c r="B8">
         <v>1119905411.7408769</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>814343125.41502714</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>155899125.67645398</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>506757257.92836487</v>
       </c>
       <c r="B9">
         <v>1195712604.7760019</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>851234931.35218334</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>175753915.01215234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>505168822.18110132</v>
       </c>
       <c r="B10">
         <v>1275571890.686219</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>890370356.43366015</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>196531395.02681574</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>503918489.12605762</v>
       </c>
       <c r="B11">
         <v>1359865264.464958</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>931891876.79550779</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>517984790.77925557</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>1023799139.8249966</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>218353769.21910724</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>770891965.30212605</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>129034272.71575028</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4549,161 +4717,187 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>570605073.91759527</v>
       </c>
       <c r="B2">
         <v>712021988.8411392</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>641313531.37936723</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>36075743.602944881</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>546556435.55415082</v>
       </c>
       <c r="B3">
         <v>752572987.22965991</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>649564711.39190531</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>52555242.774364598</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>528200806.70503402</v>
       </c>
       <c r="B4">
         <v>787869354.32156754</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>658035080.51330078</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>66241976.432789162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>512577784.94685572</v>
       </c>
       <c r="B5">
         <v>820877109.62421489</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>666727447.28553534</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>78647786.907489568</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>498585680.4414829</v>
       </c>
       <c r="B6">
         <v>852703034.15588212</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>675644357.29868245</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>90336059.621020243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>485682110.78003752</v>
       </c>
       <c r="B7">
         <v>883894056.16960812</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>684788083.47482276</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>101584679.94631906</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>473558407.78072792</v>
       </c>
       <c r="B8">
         <v>914762825.56934071</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>694160616.67503428</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>112552147.3950543</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>462022405.12783933</v>
       </c>
       <c r="B9">
         <v>945504908.17209661</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>703763656.64996791</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>123337373.22557586</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>450946952.81506598</v>
       </c>
       <c r="B10">
         <v>976250253.89310932</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>713598603.35408759</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>134005944.15256211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>440244172.18203962</v>
       </c>
       <c r="B11">
         <v>1007088925.104229</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>723666548.64313436</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>496897983.02508289</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>865354544.30808473</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>144603253.29647684</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>681126263.6665839</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>93994020.735459611</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4712,143 +4906,184 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>151905241.58038071</v>
       </c>
       <c r="B2">
         <v>239577204.00124341</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>195741222.79081208</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>22365296.535934355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>136461943.51271439</v>
       </c>
       <c r="B3">
         <v>288904036.91733217</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>212682990.21502328</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>38888289.133831069</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>114045264.6782148</v>
       </c>
       <c r="B4">
         <v>370114448.41798627</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>242079856.54810053</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>65323771.362186603</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>90252569.704395846</v>
       </c>
       <c r="B5">
         <v>458930348.94241369</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>274591459.32340479</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>94050453.88724944</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>65912540.766366363</v>
       </c>
       <c r="B6">
         <v>574056567.33353531</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>319984554.04995084</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>129628578.20591044</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>43127541.385232568</v>
       </c>
       <c r="B7">
         <v>705954510.04519236</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>374541025.71521246</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>169088512.41325507</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>23598513.649045091</v>
       </c>
       <c r="B8">
         <v>864360605.90164208</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>443979559.7753436</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>214480125.57464209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8988406.4510310721</v>
       </c>
       <c r="B9">
         <v>1045924562.597692</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>527456484.52436155</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>264524529.62925023</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1001479.754194712</v>
       </c>
       <c r="B10">
         <v>1256328160.0249071</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>628664819.88955092</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>320236398.02824295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1278232.492485841</v>
       </c>
       <c r="B11">
         <v>1495074334.663096</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>748176283.57779086</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>381070434.22719646</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f>AVERAGE(A2:A11)</f>
         <v>63657173.397406146</v>
@@ -4857,15 +5092,9 @@
         <f>AVERAGE(B2:B11)</f>
         <v>729922477.88450408</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
+      <c r="C13" s="4">
+        <f>AVERAGE(C2:C11)</f>
         <v>396789825.64095503</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>169965638.89976993</v>
       </c>
     </row>
   </sheetData>
@@ -4875,161 +5104,187 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>211403260.01881739</v>
       </c>
       <c r="B2">
         <v>252940083.3603006</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>232171671.68955898</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>10596128.403439602</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>208856647.25570789</v>
       </c>
       <c r="B3">
         <v>303936532.15251517</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>256396589.70411152</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>24255072.677756969</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>200898755.51546949</v>
       </c>
       <c r="B4">
         <v>363423456.81929737</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>282161106.16738343</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>41460382.98567038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>188469763.52293101</v>
       </c>
       <c r="B5">
         <v>431025210.27462173</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>309747486.89877635</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>61876389.477472126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>172308767.418744</v>
       </c>
       <c r="B6">
         <v>506523585.42713439</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>339416176.42293918</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>85258882.144997552</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>153059748.41270599</v>
       </c>
       <c r="B7">
         <v>589779079.34529769</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>371419413.87900186</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>111407992.58484481</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>131334057.0045342</v>
       </c>
       <c r="B8">
         <v>680693794.88016808</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>406013925.94235116</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>140142790.27439639</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>107756723.55536941</v>
       </c>
       <c r="B9">
         <v>779193758.36140025</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>443475240.95838481</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>171284957.85868135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>83015401.090449125</v>
       </c>
       <c r="B10">
         <v>885219822.80726838</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>484117611.94885874</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>204643985.13184166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>57933752.088722207</v>
       </c>
       <c r="B11">
         <v>998722648.43545532</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>528328200.26208878</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>151503687.58834505</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>579145797.18634582</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>239997167.4353911</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>365324742.38734549</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>109092374.89744915</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5038,167 +5293,192 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>247261081.24249551</v>
       </c>
       <c r="B2">
         <v>668711630.97059476</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>457986356.10654515</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>107512895.33880082</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>197768228.86693519</v>
       </c>
       <c r="B3">
         <v>810633988.61219323</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>504201108.73956418</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>156343306.05746379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>174825189.23867741</v>
       </c>
       <c r="B4">
         <v>919869439.18637204</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>547347314.21252477</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>190062308.66012615</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>154608386.45836771</v>
       </c>
       <c r="B5">
         <v>1042625820.562032</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>598617103.51019979</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>226535059.72032255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>134237518.08333459</v>
       </c>
       <c r="B6">
         <v>1175631224.0320301</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>654934371.05768239</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>265661659.68078965</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>115665666.1817659</v>
       </c>
       <c r="B7">
         <v>1313492788.0105519</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>714579227.09615886</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>305568143.32366991</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>98792333.830466211</v>
       </c>
       <c r="B8">
         <v>1458229675.7044909</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>778511004.76747859</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>346795240.27398586</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>83133859.166098088</v>
       </c>
       <c r="B9">
         <v>1611380998.66399</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>847257428.91504407</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>389858964.1576255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>68628718.481991574</v>
       </c>
       <c r="B10">
         <v>1773063836.501817</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>920846277.49190426</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>434804877.04587382</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>55327890.063936763</v>
       </c>
       <c r="B11">
         <v>1943511990.9258599</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>999419940.49489832</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>133024887.16140687</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>1271715139.3169932</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>481679617.56681716</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>702370013.2392</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>290482207.18254757</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5207,161 +5487,187 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>15606210.17351607</v>
       </c>
       <c r="B2">
         <v>39449727.696229212</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>27527968.934872642</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>6082529.9802839644</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>11550680.10724384</v>
       </c>
       <c r="B3">
         <v>47723828.221244819</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>29637254.164244331</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>9227843.9066329021</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8463058.944489466</v>
       </c>
       <c r="B4">
         <v>55849318.35336896</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>32156188.648929212</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>12088331.481857015</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5946849.4759663558</v>
       </c>
       <c r="B5">
         <v>64308511.223516516</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>35127680.349741437</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>14888179.017232183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3887788.5696554538</v>
       </c>
       <c r="B6">
         <v>73301485.885334834</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>38594637.227495141</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>17707575.84583658</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2254283.6558757699</v>
       </c>
       <c r="B7">
         <v>82945650.8301332</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>42599967.243004486</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>20584532.442412611</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1048378.729640061</v>
       </c>
       <c r="B8">
         <v>93324777.984527171</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>47186578.357083619</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>23539897.769103855</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>288418.11666728382</v>
       </c>
       <c r="B9">
         <v>104506338.9444261</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>52397378.530546695</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>26586204.292795617</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1567.8178362311489</v>
       </c>
       <c r="B10">
         <v>116548983.6305794</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>58275275.724207811</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>29731483.625699788</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>220145.98263171711</v>
       </c>
       <c r="B11">
         <v>129506209.81513061</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>64863177.89888116</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>4926738.1573522259</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>80746483.258449078</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>32981138.73278033</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>42836610.707900658</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>19341771.709463481</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5370,161 +5676,187 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>190948844.07116279</v>
       </c>
       <c r="B2">
         <v>560668762.91228616</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D11" si="0">AVERAGE(A2:B2)</f>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">AVERAGE(A2:B2)</f>
         <v>375808803.49172449</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4">
+        <f>(B2-C2)/1.96</f>
+        <v>94316305.826817185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>158982392.35144421</v>
       </c>
       <c r="B3">
         <v>656639443.69823086</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <f t="shared" si="0"/>
         <v>407810918.02483755</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D11" si="1">(B3-C3)/1.96</f>
+        <v>126953329.42520067</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>151311679.9446007</v>
       </c>
       <c r="B4">
         <v>734748895.59781075</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>443030287.77120572</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>148836024.4013291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>144568843.93537959</v>
       </c>
       <c r="B5">
         <v>833845846.65265334</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>489207345.29401648</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>175835970.08093718</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>135936333.51880071</v>
       </c>
       <c r="B6">
         <v>935183993.09773898</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>535560163.30826986</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>203889709.07625976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>128974444.51362661</v>
       </c>
       <c r="B7">
         <v>1035702010.497537</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>582338227.50558186</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>231308052.54691589</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>123252406.44158401</v>
       </c>
       <c r="B8">
         <v>1140865505.156076</v>
       </c>
-      <c r="D8">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>632058955.79883003</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>259595178.24349281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>117854670.1636892</v>
       </c>
       <c r="B9">
         <v>1250573329.867188</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>684214000.01543856</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>288958841.76109666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>112790961.9868522</v>
       </c>
       <c r="B10">
         <v>1363909117.3884921</v>
       </c>
-      <c r="D10">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>738350039.68767214</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>319162794.74531633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>108100068.2739616</v>
       </c>
       <c r="B11">
         <v>1481295234.0425</v>
       </c>
-      <c r="D11">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>794697651.15823078</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>AVERAGE(A2:A11)</f>
-        <v>137272064.52011016</v>
-      </c>
-      <c r="B13" s="4">
-        <f>AVERAGE(B2:B11)</f>
-        <v>999343213.89105129</v>
-      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>350304889.226668</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4">
-        <f>AVERAGE(D2:D11)</f>
-        <v>568307639.20558083</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
-        <f>(B13-D13)/1.96</f>
-        <v>219916109.53340331</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DATA/antigen_CI_Random_generator.xlsx
+++ b/DATA/antigen_CI_Random_generator.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="590" documentId="11_4A5645C871AEA98286DE389EAFF8EF0F542BC54D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2937F37B-86E6-431C-A5C2-8E05EA8207B0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diphtheria" sheetId="1" r:id="rId1"/>
@@ -336,34 +336,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>610366749.10346115</c:v>
+                  <c:v>457122853.94701272</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>531163244.01083982</c:v>
+                  <c:v>503275270.29348505</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>799734080.94260573</c:v>
+                  <c:v>553795129.57356727</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>582478519.84207511</c:v>
+                  <c:v>602676362.11355364</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>585579461.66020167</c:v>
+                  <c:v>758520641.55148876</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>795043869.14612949</c:v>
+                  <c:v>634808322.84006441</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>777274926.59863842</c:v>
+                  <c:v>894980182.61206615</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>812112294.92690504</c:v>
+                  <c:v>1014224977.9584821</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>916431319.59162045</c:v>
+                  <c:v>980127111.33085465</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>788606590.24584341</c:v>
+                  <c:v>928665061.87106824</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -408,34 +408,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>20151026.863962889</c:v>
+                  <c:v>31156072.503887001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25356646.942508951</c:v>
+                  <c:v>28367064.522340223</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27543029.649350435</c:v>
+                  <c:v>26151006.728743546</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37009863.591849729</c:v>
+                  <c:v>29496750.165311635</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>36017326.664739236</c:v>
+                  <c:v>36595295.120902337</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>41641280.211628623</c:v>
+                  <c:v>38112921.564927906</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38600796.984534249</c:v>
+                  <c:v>50569112.567016758</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46346411.309301585</c:v>
+                  <c:v>46137534.85300564</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>52122361.570719413</c:v>
+                  <c:v>64293758.063007638</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>63584922.777330749</c:v>
+                  <c:v>70172625.677746937</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -480,34 +480,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>269979741.65914881</c:v>
+                  <c:v>298095721.07854128</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>424620184.82685202</c:v>
+                  <c:v>398478103.28823358</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>458445881.5196749</c:v>
+                  <c:v>711762189.28609896</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>441303051.16330719</c:v>
+                  <c:v>518976399.13094008</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>518738648.8944546</c:v>
+                  <c:v>642162313.27672553</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560590321.12412798</c:v>
+                  <c:v>718724385.09488463</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>619263506.51350164</c:v>
+                  <c:v>691224688.01780987</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>597953201.04888475</c:v>
+                  <c:v>654650002.44740343</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>741556488.15382314</c:v>
+                  <c:v>666920034.31631446</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>763885830.22618496</c:v>
+                  <c:v>865825795.92512167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -552,34 +552,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>742785491.46924627</c:v>
+                  <c:v>677023497.45828068</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>752853587.4273622</c:v>
+                  <c:v>683229740.30633855</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>846484448.36472392</c:v>
+                  <c:v>817518417.19670308</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>911331567.75979292</c:v>
+                  <c:v>890594656.53506279</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>904479481.78190124</c:v>
+                  <c:v>939871879.58393037</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1164816092.3500228</c:v>
+                  <c:v>1163224184.0391212</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1458084052.6528018</c:v>
+                  <c:v>1443366623.7817435</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1527318076.5038919</c:v>
+                  <c:v>1673641276.2313941</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1591242235.5884593</c:v>
+                  <c:v>1565260717.6774495</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1920616477.7595139</c:v>
+                  <c:v>1786830973.3253071</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -624,34 +624,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>602773484.32235479</c:v>
+                  <c:v>671869414.68780088</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>640837760.7040205</c:v>
+                  <c:v>678277910.89305747</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>685019527.58840501</c:v>
+                  <c:v>640142293.25159991</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>628349818.47549438</c:v>
+                  <c:v>660321107.94923842</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>641662353.09790337</c:v>
+                  <c:v>633614246.03202999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>679487017.55810404</c:v>
+                  <c:v>772317965.51780128</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>652578957.22678268</c:v>
+                  <c:v>670874344.72589874</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>663703060.87461042</c:v>
+                  <c:v>748693436.75190592</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>691493859.20329762</c:v>
+                  <c:v>677967265.17084277</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>652692515.10939085</c:v>
+                  <c:v>722016955.70364547</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -696,34 +696,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>362422627.99443895</c:v>
+                  <c:v>377275718.16613919</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>315701250.17060524</c:v>
+                  <c:v>372137409.08397961</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>368472445.85273087</c:v>
+                  <c:v>348053062.2402299</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>317119649.02451921</c:v>
+                  <c:v>360480876.08980185</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>376239025.84218717</c:v>
+                  <c:v>331827976.45623082</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>374412379.16049558</c:v>
+                  <c:v>330756169.81888652</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>356424154.96221793</c:v>
+                  <c:v>360902134.27739215</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>387528371.29742432</c:v>
+                  <c:v>388885875.51419872</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>357256293.51931</c:v>
+                  <c:v>402237354.26486325</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>350848044.49634397</c:v>
+                  <c:v>377135973.27511346</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -770,34 +770,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>395303027.42456394</c:v>
+                  <c:v>375153099.97555006</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>408220393.14708143</c:v>
+                  <c:v>399113630.95474243</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>444641915.07728684</c:v>
+                  <c:v>359084337.29367602</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>453827503.85857785</c:v>
+                  <c:v>421580866.27530158</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>383013545.72927064</c:v>
+                  <c:v>329371252.91806728</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>379502006.21421438</c:v>
+                  <c:v>381002007.08612812</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>401255114.97082168</c:v>
+                  <c:v>351949630.52484924</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>444774444.58579254</c:v>
+                  <c:v>392146414.97037613</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>403463446.28985393</c:v>
+                  <c:v>413178484.58318436</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>467796355.77015615</c:v>
+                  <c:v>398402047.61702693</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -844,34 +844,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>314257258.63745034</c:v>
+                  <c:v>321021498.77043068</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>314152799.93181235</c:v>
+                  <c:v>324852068.52688533</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>350041789.64064449</c:v>
+                  <c:v>333828730.00548226</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>301268334.68733639</c:v>
+                  <c:v>329998445.03929907</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>352128748.55086374</c:v>
+                  <c:v>374935935.10480356</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>355668888.58184254</c:v>
+                  <c:v>374045908.13470089</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>398675396.96262902</c:v>
+                  <c:v>387779792.11458975</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>427391965.79788744</c:v>
+                  <c:v>389432695.59690118</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>352020151.85880196</c:v>
+                  <c:v>395335860.46782255</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>434381232.9750579</c:v>
+                  <c:v>441997400.83768731</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -918,34 +918,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>562510067.91676295</c:v>
+                  <c:v>642257347.02621889</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>686050307.64316642</c:v>
+                  <c:v>696375118.95304465</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>575413534.3232224</c:v>
+                  <c:v>699522239.88239527</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>687383594.87407196</c:v>
+                  <c:v>713196818.47858298</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>697755472.33727348</c:v>
+                  <c:v>685766669.14306688</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>780317577.12405515</c:v>
+                  <c:v>894009291.88586974</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>749736107.30519927</c:v>
+                  <c:v>777360922.36234915</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>870930380.34278071</c:v>
+                  <c:v>917137512.60400784</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>907526188.16005743</c:v>
+                  <c:v>846698697.37109864</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>892368067.98188782</c:v>
+                  <c:v>888472934.35479891</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -992,34 +992,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>29375908.204356764</c:v>
+                  <c:v>29941818.059163366</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36973240.974811286</c:v>
+                  <c:v>35945626.474653319</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>42810635.44118131</c:v>
+                  <c:v>39295764.392632052</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46450943.908866525</c:v>
+                  <c:v>48422770.210406207</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55751458.96213802</c:v>
+                  <c:v>54601763.314007938</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>58567348.47724364</c:v>
+                  <c:v>58092583.49952545</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>67149671.127208233</c:v>
+                  <c:v>67108007.357160173</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>71955815.934473842</c:v>
+                  <c:v>74338629.158265382</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>81054530.296169713</c:v>
+                  <c:v>81068109.129203558</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>89313131.797970936</c:v>
+                  <c:v>88939621.771273941</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1066,34 +1066,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>225177168.58647105</c:v>
+                  <c:v>209593325.68123284</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>211818559.40818676</c:v>
+                  <c:v>195966077.850734</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>197255863.65012899</c:v>
+                  <c:v>227277618.646478</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>292473628.34834433</c:v>
+                  <c:v>259852058.96648291</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>338275388.45804477</c:v>
+                  <c:v>322776130.15048355</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>381248305.86100721</c:v>
+                  <c:v>346186034.79188496</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>444205575.87645489</c:v>
+                  <c:v>462262560.34396815</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>529896172.87651294</c:v>
+                  <c:v>517488113.05277401</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>663705067.16484177</c:v>
+                  <c:v>609537918.88273335</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>735092352.48062396</c:v>
+                  <c:v>714702627.20747411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1140,34 +1140,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>241071149.45158824</c:v>
+                  <c:v>232765581.05368111</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>254015380.07613316</c:v>
+                  <c:v>253540537.92330924</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>290306034.27144468</c:v>
+                  <c:v>274389553.50016904</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>306939644.52600533</c:v>
+                  <c:v>309079668.52331275</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>336686422.01807326</c:v>
+                  <c:v>347500177.60982418</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>369304271.70029795</c:v>
+                  <c:v>374213031.4678508</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>410655800.2244851</c:v>
+                  <c:v>394696124.35456306</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>442999496.19893312</c:v>
+                  <c:v>459739135.39224821</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>475584022.34082985</c:v>
+                  <c:v>490499877.32620466</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>454731642.6732856</c:v>
+                  <c:v>421602194.88334519</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1978,10 +1978,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3080,43 +3076,43 @@
       </c>
       <c r="B2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C2,Measles!$D$2)</f>
-        <v>610366749.10346115</v>
+        <v>457122853.94701272</v>
       </c>
       <c r="C2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C3,Measles!$D$2)</f>
-        <v>531163244.01083982</v>
+        <v>503275270.29348505</v>
       </c>
       <c r="D2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C4,Measles!$D$2)</f>
-        <v>799734080.94260573</v>
+        <v>553795129.57356727</v>
       </c>
       <c r="E2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C5,Measles!$D$2)</f>
-        <v>582478519.84207511</v>
+        <v>602676362.11355364</v>
       </c>
       <c r="F2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C6,Measles!$D$2)</f>
-        <v>585579461.66020167</v>
+        <v>758520641.55148876</v>
       </c>
       <c r="G2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C7,Measles!$D$2)</f>
-        <v>795043869.14612949</v>
+        <v>634808322.84006441</v>
       </c>
       <c r="H2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C8,Measles!$D$2)</f>
-        <v>777274926.59863842</v>
+        <v>894980182.61206615</v>
       </c>
       <c r="I2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C9,Measles!$D$2)</f>
-        <v>812112294.92690504</v>
+        <v>1014224977.9584821</v>
       </c>
       <c r="J2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C10,Measles!$D$2)</f>
-        <v>916431319.59162045</v>
+        <v>980127111.33085465</v>
       </c>
       <c r="K2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$C11,Measles!$D$2)</f>
-        <v>788606590.24584341</v>
+        <v>928665061.87106824</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -3125,43 +3121,43 @@
       </c>
       <c r="B3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C2,Mumps!$D$2)</f>
-        <v>20151026.863962889</v>
+        <v>31156072.503887001</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C3,Mumps!$D$2)</f>
-        <v>25356646.942508951</v>
+        <v>28367064.522340223</v>
       </c>
       <c r="D3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C4,Mumps!$D$2)</f>
-        <v>27543029.649350435</v>
+        <v>26151006.728743546</v>
       </c>
       <c r="E3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C5,Mumps!$D$2)</f>
-        <v>37009863.591849729</v>
+        <v>29496750.165311635</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C6,Mumps!$D$2)</f>
-        <v>36017326.664739236</v>
+        <v>36595295.120902337</v>
       </c>
       <c r="G3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C7,Mumps!$D$2)</f>
-        <v>41641280.211628623</v>
+        <v>38112921.564927906</v>
       </c>
       <c r="H3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C8,Mumps!$D$2)</f>
-        <v>38600796.984534249</v>
+        <v>50569112.567016758</v>
       </c>
       <c r="I3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C9,Mumps!$D$2)</f>
-        <v>46346411.309301585</v>
+        <v>46137534.85300564</v>
       </c>
       <c r="J3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C10,Mumps!$D$2)</f>
-        <v>52122361.570719413</v>
+        <v>64293758.063007638</v>
       </c>
       <c r="K3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$C11,Mumps!$D$2)</f>
-        <v>63584922.777330749</v>
+        <v>70172625.677746937</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -3170,43 +3166,43 @@
       </c>
       <c r="B4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C2,Rubella!$D$2)</f>
-        <v>269979741.65914881</v>
+        <v>298095721.07854128</v>
       </c>
       <c r="C4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C3,Rubella!$D$2)</f>
-        <v>424620184.82685202</v>
+        <v>398478103.28823358</v>
       </c>
       <c r="D4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C4,Rubella!$D$2)</f>
-        <v>458445881.5196749</v>
+        <v>711762189.28609896</v>
       </c>
       <c r="E4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C5,Rubella!$D$2)</f>
-        <v>441303051.16330719</v>
+        <v>518976399.13094008</v>
       </c>
       <c r="F4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C6,Rubella!$D$2)</f>
-        <v>518738648.8944546</v>
+        <v>642162313.27672553</v>
       </c>
       <c r="G4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C7,Rubella!$D$2)</f>
-        <v>560590321.12412798</v>
+        <v>718724385.09488463</v>
       </c>
       <c r="H4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C8,Rubella!$D$2)</f>
-        <v>619263506.51350164</v>
+        <v>691224688.01780987</v>
       </c>
       <c r="I4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C9,Rubella!$D$2)</f>
-        <v>597953201.04888475</v>
+        <v>654650002.44740343</v>
       </c>
       <c r="J4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C10,Rubella!$D$2)</f>
-        <v>741556488.15382314</v>
+        <v>666920034.31631446</v>
       </c>
       <c r="K4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$C11,Rubella!$D$2)</f>
-        <v>763885830.22618496</v>
+        <v>865825795.92512167</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -3215,43 +3211,43 @@
       </c>
       <c r="B5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C2,Diphtheria!$D$2)</f>
-        <v>742785491.46924627</v>
+        <v>677023497.45828068</v>
       </c>
       <c r="C5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C3,Diphtheria!$D$2)</f>
-        <v>752853587.4273622</v>
+        <v>683229740.30633855</v>
       </c>
       <c r="D5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C4,Diphtheria!$D$2)</f>
-        <v>846484448.36472392</v>
+        <v>817518417.19670308</v>
       </c>
       <c r="E5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C5,Diphtheria!$D$2)</f>
-        <v>911331567.75979292</v>
+        <v>890594656.53506279</v>
       </c>
       <c r="F5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C6,Diphtheria!$D$2)</f>
-        <v>904479481.78190124</v>
+        <v>939871879.58393037</v>
       </c>
       <c r="G5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C8,Diphtheria!$D$2)</f>
-        <v>1164816092.3500228</v>
+        <v>1163224184.0391212</v>
       </c>
       <c r="H5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C9,Diphtheria!$D$2)</f>
-        <v>1458084052.6528018</v>
+        <v>1443366623.7817435</v>
       </c>
       <c r="I5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C10,Diphtheria!$D$2)</f>
-        <v>1527318076.5038919</v>
+        <v>1673641276.2313941</v>
       </c>
       <c r="J5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C10,Diphtheria!$D$2)</f>
-        <v>1591242235.5884593</v>
+        <v>1565260717.6774495</v>
       </c>
       <c r="K5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$C11,Diphtheria!$D$2)</f>
-        <v>1920616477.7595139</v>
+        <v>1786830973.3253071</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -3260,43 +3256,43 @@
       </c>
       <c r="B6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C2,Tetanus!$D$2)</f>
-        <v>602773484.32235479</v>
+        <v>671869414.68780088</v>
       </c>
       <c r="C6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C3,Tetanus!$D$2)</f>
-        <v>640837760.7040205</v>
+        <v>678277910.89305747</v>
       </c>
       <c r="D6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C4,Tetanus!$D$2)</f>
-        <v>685019527.58840501</v>
+        <v>640142293.25159991</v>
       </c>
       <c r="E6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C5,Tetanus!$D$2)</f>
-        <v>628349818.47549438</v>
+        <v>660321107.94923842</v>
       </c>
       <c r="F6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C6,Tetanus!$D$2)</f>
-        <v>641662353.09790337</v>
+        <v>633614246.03202999</v>
       </c>
       <c r="G6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C7,Tetanus!$D$2)</f>
-        <v>679487017.55810404</v>
+        <v>772317965.51780128</v>
       </c>
       <c r="H6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C8,Tetanus!$D$2)</f>
-        <v>652578957.22678268</v>
+        <v>670874344.72589874</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C9,Tetanus!$D$2)</f>
-        <v>663703060.87461042</v>
+        <v>748693436.75190592</v>
       </c>
       <c r="J6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C10,Tetanus!$D$2)</f>
-        <v>691493859.20329762</v>
+        <v>677967265.17084277</v>
       </c>
       <c r="K6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$C11,Tetanus!$D$2)</f>
-        <v>652692515.10939085</v>
+        <v>722016955.70364547</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -3305,43 +3301,43 @@
       </c>
       <c r="B7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C2,Pertussis!$D$2)</f>
-        <v>362422627.99443895</v>
+        <v>377275718.16613919</v>
       </c>
       <c r="C7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C2,Pertussis!$D$2)</f>
-        <v>315701250.17060524</v>
+        <v>372137409.08397961</v>
       </c>
       <c r="D7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C4,Pertussis!$D$2)</f>
-        <v>368472445.85273087</v>
+        <v>348053062.2402299</v>
       </c>
       <c r="E7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C5,Pertussis!$D$2)</f>
-        <v>317119649.02451921</v>
+        <v>360480876.08980185</v>
       </c>
       <c r="F7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C6,Pertussis!$D$2)</f>
-        <v>376239025.84218717</v>
+        <v>331827976.45623082</v>
       </c>
       <c r="G7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C7,Pertussis!$D$2)</f>
-        <v>374412379.16049558</v>
+        <v>330756169.81888652</v>
       </c>
       <c r="H7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C8,Pertussis!$D$2)</f>
-        <v>356424154.96221793</v>
+        <v>360902134.27739215</v>
       </c>
       <c r="I7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C9,Pertussis!$D$2)</f>
-        <v>387528371.29742432</v>
+        <v>388885875.51419872</v>
       </c>
       <c r="J7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C10,Pertussis!$D$2)</f>
-        <v>357256293.51931</v>
+        <v>402237354.26486325</v>
       </c>
       <c r="K7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$C11,Pertussis!$D$2)</f>
-        <v>350848044.49634397</v>
+        <v>377135973.27511346</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -3350,43 +3346,43 @@
       </c>
       <c r="B8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C2,Hepatitis_B!$D$2)</f>
-        <v>395303027.42456394</v>
+        <v>375153099.97555006</v>
       </c>
       <c r="C8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C3,Hepatitis_B!$D$2)</f>
-        <v>408220393.14708143</v>
+        <v>399113630.95474243</v>
       </c>
       <c r="D8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C4,Hepatitis_B!$D$2)</f>
-        <v>444641915.07728684</v>
+        <v>359084337.29367602</v>
       </c>
       <c r="E8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C5,Hepatitis_B!$D$2)</f>
-        <v>453827503.85857785</v>
+        <v>421580866.27530158</v>
       </c>
       <c r="F8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C6,Hepatitis_B!$D$2)</f>
-        <v>383013545.72927064</v>
+        <v>329371252.91806728</v>
       </c>
       <c r="G8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C7,Hepatitis_B!$D$2)</f>
-        <v>379502006.21421438</v>
+        <v>381002007.08612812</v>
       </c>
       <c r="H8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C8,Hepatitis_B!$D$2)</f>
-        <v>401255114.97082168</v>
+        <v>351949630.52484924</v>
       </c>
       <c r="I8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C9,Hepatitis_B!$D$2)</f>
-        <v>444774444.58579254</v>
+        <v>392146414.97037613</v>
       </c>
       <c r="J8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C10,Hepatitis_B!$D$2)</f>
-        <v>403463446.28985393</v>
+        <v>413178484.58318436</v>
       </c>
       <c r="K8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C11,Hepatitis_B!$D$2)</f>
-        <v>467796355.77015615</v>
+        <v>398402047.61702693</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -3395,43 +3391,43 @@
       </c>
       <c r="B9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C2,Hib!$D$2)</f>
-        <v>314257258.63745034</v>
+        <v>321021498.77043068</v>
       </c>
       <c r="C9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C3,Hib!$D$2)</f>
-        <v>314152799.93181235</v>
+        <v>324852068.52688533</v>
       </c>
       <c r="D9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C4,Hib!$D$2)</f>
-        <v>350041789.64064449</v>
+        <v>333828730.00548226</v>
       </c>
       <c r="E9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C5,Hib!$D$2)</f>
-        <v>301268334.68733639</v>
+        <v>329998445.03929907</v>
       </c>
       <c r="F9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C6,Hib!$D$2)</f>
-        <v>352128748.55086374</v>
+        <v>374935935.10480356</v>
       </c>
       <c r="G9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C7,Hib!$D$2)</f>
-        <v>355668888.58184254</v>
+        <v>374045908.13470089</v>
       </c>
       <c r="H9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C8,Hib!$D$2)</f>
-        <v>398675396.96262902</v>
+        <v>387779792.11458975</v>
       </c>
       <c r="I9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C9,Hib!$D$2)</f>
-        <v>427391965.79788744</v>
+        <v>389432695.59690118</v>
       </c>
       <c r="J9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C10,Hib!$D$2)</f>
-        <v>352020151.85880196</v>
+        <v>395335860.46782255</v>
       </c>
       <c r="K9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$C11,Hib!$D$2)</f>
-        <v>434381232.9750579</v>
+        <v>441997400.83768731</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -3440,43 +3436,43 @@
       </c>
       <c r="B10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C2,Polio!$D$2)</f>
-        <v>562510067.91676295</v>
+        <v>642257347.02621889</v>
       </c>
       <c r="C10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C3,Polio!$D$2)</f>
-        <v>686050307.64316642</v>
+        <v>696375118.95304465</v>
       </c>
       <c r="D10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C4,Polio!$D$2)</f>
-        <v>575413534.3232224</v>
+        <v>699522239.88239527</v>
       </c>
       <c r="E10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C5,Polio!$D$2)</f>
-        <v>687383594.87407196</v>
+        <v>713196818.47858298</v>
       </c>
       <c r="F10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C6,Polio!$D$2)</f>
-        <v>697755472.33727348</v>
+        <v>685766669.14306688</v>
       </c>
       <c r="G10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C7,Polio!$D$2)</f>
-        <v>780317577.12405515</v>
+        <v>894009291.88586974</v>
       </c>
       <c r="H10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C8,Polio!$D$2)</f>
-        <v>749736107.30519927</v>
+        <v>777360922.36234915</v>
       </c>
       <c r="I10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C9,Polio!$D$2)</f>
-        <v>870930380.34278071</v>
+        <v>917137512.60400784</v>
       </c>
       <c r="J10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C10,Polio!$D$2)</f>
-        <v>907526188.16005743</v>
+        <v>846698697.37109864</v>
       </c>
       <c r="K10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$C11,Polio!$D$2)</f>
-        <v>892368067.98188782</v>
+        <v>888472934.35479891</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -3485,43 +3481,43 @@
       </c>
       <c r="B11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C2,HPV!$D$2)</f>
-        <v>29375908.204356764</v>
+        <v>29941818.059163366</v>
       </c>
       <c r="C11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C3,HPV!$D$2)</f>
-        <v>36973240.974811286</v>
+        <v>35945626.474653319</v>
       </c>
       <c r="D11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C4,HPV!$D$2)</f>
-        <v>42810635.44118131</v>
+        <v>39295764.392632052</v>
       </c>
       <c r="E11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C5,HPV!$D$2)</f>
-        <v>46450943.908866525</v>
+        <v>48422770.210406207</v>
       </c>
       <c r="F11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C6,HPV!$D$2)</f>
-        <v>55751458.96213802</v>
+        <v>54601763.314007938</v>
       </c>
       <c r="G11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C7,HPV!$D$2)</f>
-        <v>58567348.47724364</v>
+        <v>58092583.49952545</v>
       </c>
       <c r="H11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C8,HPV!$D$2)</f>
-        <v>67149671.127208233</v>
+        <v>67108007.357160173</v>
       </c>
       <c r="I11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C9,HPV!$D$2)</f>
-        <v>71955815.934473842</v>
+        <v>74338629.158265382</v>
       </c>
       <c r="J11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C10,HPV!$D$2)</f>
-        <v>81054530.296169713</v>
+        <v>81068109.129203558</v>
       </c>
       <c r="K11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$C11,HPV!$D$2)</f>
-        <v>89313131.797970936</v>
+        <v>88939621.771273941</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -3530,43 +3526,43 @@
       </c>
       <c r="B12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C2,Rotavirus!$D$2)</f>
-        <v>225177168.58647105</v>
+        <v>209593325.68123284</v>
       </c>
       <c r="C12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C3,Rotavirus!$D$2)</f>
-        <v>211818559.40818676</v>
+        <v>195966077.850734</v>
       </c>
       <c r="D12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C4,Rotavirus!$D$2)</f>
-        <v>197255863.65012899</v>
+        <v>227277618.646478</v>
       </c>
       <c r="E12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C5,Rotavirus!$D$2)</f>
-        <v>292473628.34834433</v>
+        <v>259852058.96648291</v>
       </c>
       <c r="F12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C6,Rotavirus!$D$2)</f>
-        <v>338275388.45804477</v>
+        <v>322776130.15048355</v>
       </c>
       <c r="G12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C7,Rotavirus!$D$2)</f>
-        <v>381248305.86100721</v>
+        <v>346186034.79188496</v>
       </c>
       <c r="H12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C8,Rotavirus!$D$2)</f>
-        <v>444205575.87645489</v>
+        <v>462262560.34396815</v>
       </c>
       <c r="I12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C9,Rotavirus!$D$2)</f>
-        <v>529896172.87651294</v>
+        <v>517488113.05277401</v>
       </c>
       <c r="J12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C10,Rotavirus!$D$2)</f>
-        <v>663705067.16484177</v>
+        <v>609537918.88273335</v>
       </c>
       <c r="K12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$C11,Rotavirus!$D$2)</f>
-        <v>735092352.48062396</v>
+        <v>714702627.20747411</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -3575,43 +3571,43 @@
       </c>
       <c r="B13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C2,PCV!$D$2)</f>
-        <v>241071149.45158824</v>
+        <v>232765581.05368111</v>
       </c>
       <c r="C13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C3,PCV!$D$2)</f>
-        <v>254015380.07613316</v>
+        <v>253540537.92330924</v>
       </c>
       <c r="D13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C4,PCV!$D$2)</f>
-        <v>290306034.27144468</v>
+        <v>274389553.50016904</v>
       </c>
       <c r="E13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C5,PCV!$D$2)</f>
-        <v>306939644.52600533</v>
+        <v>309079668.52331275</v>
       </c>
       <c r="F13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C6,PCV!$D$2)</f>
-        <v>336686422.01807326</v>
+        <v>347500177.60982418</v>
       </c>
       <c r="G13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C7,PCV!$D$2)</f>
-        <v>369304271.70029795</v>
+        <v>374213031.4678508</v>
       </c>
       <c r="H13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C8,PCV!$D$2)</f>
-        <v>410655800.2244851</v>
+        <v>394696124.35456306</v>
       </c>
       <c r="I13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C9,PCV!$D$2)</f>
-        <v>442999496.19893312</v>
+        <v>459739135.39224821</v>
       </c>
       <c r="J13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$C10,PCV!$D$2)</f>
-        <v>475584022.34082985</v>
+        <v>490499877.32620466</v>
       </c>
       <c r="K13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$C11,PCV!$D$2)</f>
-        <v>454731642.6732856</v>
+        <v>421602194.88334519</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -3620,43 +3616,43 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(B2&gt;Measles!B2,Measles!B2,IF(Scenario_data!B2 &lt;Measles!A2,Measles!A2,Scenario_data!B2))</f>
-        <v>610366749.10346115</v>
+        <v>457122853.94701272</v>
       </c>
       <c r="C15" s="7">
         <f ca="1">IF(C2&gt;Measles!B3,Measles!B3,IF(Scenario_data!C2 &lt;Measles!A3,Measles!A3,Scenario_data!C2))</f>
-        <v>531163244.01083982</v>
+        <v>503275270.29348505</v>
       </c>
       <c r="D15" s="7">
         <f ca="1">IF(D2&gt;Measles!B4,Measles!B4,IF(Scenario_data!D2 &lt;Measles!A4,Measles!A4,Scenario_data!D2))</f>
-        <v>799734080.94260573</v>
+        <v>553795129.57356727</v>
       </c>
       <c r="E15" s="7">
         <f ca="1">IF(E2&gt;Measles!B5,Measles!B5,IF(Scenario_data!E2 &lt;Measles!A5,Measles!A5,Scenario_data!E2))</f>
-        <v>582478519.84207511</v>
+        <v>602676362.11355364</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">IF(F2&gt;Measles!B6,Measles!B6,IF(Scenario_data!F2 &lt;Measles!A6,Measles!A6,Scenario_data!F2))</f>
-        <v>585579461.66020167</v>
+        <v>758520641.55148876</v>
       </c>
       <c r="G15" s="7">
         <f ca="1">IF(G2&gt;Measles!B7,Measles!B7,IF(Scenario_data!G2 &lt;Measles!A7,Measles!A7,Scenario_data!G2))</f>
-        <v>795043869.14612949</v>
+        <v>634808322.84006441</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">IF(H2&gt;Measles!B8,Measles!B8,IF(Scenario_data!H2 &lt;Measles!A8,Measles!A8,Scenario_data!H2))</f>
-        <v>777274926.59863842</v>
+        <v>894980182.61206615</v>
       </c>
       <c r="I15" s="7">
         <f ca="1">IF(I2&gt;Measles!B9,Measles!B9,IF(Scenario_data!I2 &lt;Measles!A9,Measles!A9,Scenario_data!I2))</f>
-        <v>812112294.92690504</v>
+        <v>1014224977.9584821</v>
       </c>
       <c r="J15" s="7">
         <f ca="1">IF(J2&gt;Measles!B10,Measles!B10,IF(Scenario_data!J2 &lt;Measles!A10,Measles!A10,Scenario_data!J2))</f>
-        <v>916431319.59162045</v>
+        <v>980127111.33085465</v>
       </c>
       <c r="K15" s="7">
         <f ca="1">IF(K2&gt;Measles!B11,Measles!B11,IF(Scenario_data!K2 &lt;Measles!A11,Measles!A11,Scenario_data!K2))</f>
-        <v>788606590.24584341</v>
+        <v>928665061.87106824</v>
       </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
@@ -3667,43 +3663,43 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(B3&gt;Mumps!B2,Mumps!B2,IF(Scenario_data!B3 &lt;Mumps!A2,Mumps!A2,Scenario_data!B3))</f>
-        <v>20151026.863962889</v>
+        <v>31156072.503887001</v>
       </c>
       <c r="C16" s="7">
         <f ca="1">IF(C3&gt;Mumps!B3,Mumps!B3,IF(Scenario_data!C3 &lt;Mumps!A3,Mumps!A3,Scenario_data!C3))</f>
-        <v>25356646.942508951</v>
+        <v>28367064.522340223</v>
       </c>
       <c r="D16" s="7">
         <f ca="1">IF(D3&gt;Mumps!B4,Mumps!B4,IF(Scenario_data!D3 &lt;Mumps!A4,Mumps!A4,Scenario_data!D3))</f>
-        <v>27543029.649350435</v>
+        <v>26151006.728743546</v>
       </c>
       <c r="E16" s="7">
         <f ca="1">IF(E3&gt;Mumps!B5,Mumps!B5,IF(Scenario_data!E3 &lt;Mumps!A5,Mumps!A5,Scenario_data!E3))</f>
-        <v>37009863.591849729</v>
+        <v>29496750.165311635</v>
       </c>
       <c r="F16" s="7">
         <f ca="1">IF(F3&gt;Mumps!B6,Mumps!B6,IF(Scenario_data!F3 &lt;Mumps!A6,Mumps!A6,Scenario_data!F3))</f>
-        <v>36017326.664739236</v>
+        <v>36595295.120902337</v>
       </c>
       <c r="G16" s="7">
         <f ca="1">IF(G3&gt;Mumps!B7,Mumps!B7,IF(Scenario_data!G3 &lt;Mumps!A7,Mumps!A7,Scenario_data!G3))</f>
-        <v>41641280.211628623</v>
+        <v>38112921.564927906</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">IF(H3&gt;Mumps!B8,Mumps!B8,IF(Scenario_data!H3 &lt;Mumps!A8,Mumps!A8,Scenario_data!H3))</f>
-        <v>38600796.984534249</v>
+        <v>50569112.567016758</v>
       </c>
       <c r="I16" s="7">
         <f ca="1">IF(I3&gt;Mumps!B9,Mumps!B9,IF(Scenario_data!I3 &lt;Mumps!A9,Mumps!A9,Scenario_data!I3))</f>
-        <v>46346411.309301585</v>
+        <v>46137534.85300564</v>
       </c>
       <c r="J16" s="7">
         <f ca="1">IF(J3&gt;Mumps!B10,Mumps!B10,IF(Scenario_data!J3 &lt;Mumps!A10,Mumps!A10,Scenario_data!J3))</f>
-        <v>52122361.570719413</v>
+        <v>64293758.063007638</v>
       </c>
       <c r="K16" s="7">
         <f ca="1">IF(K3&gt;Mumps!B11,Mumps!B11,IF(Scenario_data!K3 &lt;Mumps!A11,Mumps!A11,Scenario_data!K3))</f>
-        <v>63584922.777330749</v>
+        <v>70172625.677746937</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -3712,43 +3708,43 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(B4&gt;Rubella!B2,Rubella!B2,IF(Scenario_data!B4 &lt;Rubella!A2,Rubella!A2,Scenario_data!B4))</f>
-        <v>269979741.65914881</v>
+        <v>298095721.07854128</v>
       </c>
       <c r="C17" s="7">
         <f ca="1">IF(C4&gt;Rubella!B3,Rubella!B3,IF(Scenario_data!C4 &lt;Rubella!A3,Rubella!A3,Scenario_data!C4))</f>
-        <v>424620184.82685202</v>
+        <v>398478103.28823358</v>
       </c>
       <c r="D17" s="7">
         <f ca="1">IF(D4&gt;Rubella!B4,Rubella!B4,IF(Scenario_data!D4 &lt;Rubella!A4,Rubella!A4,Scenario_data!D4))</f>
-        <v>458445881.5196749</v>
+        <v>711762189.28609896</v>
       </c>
       <c r="E17" s="7">
         <f ca="1">IF(E4&gt;Rubella!B5,Rubella!B5,IF(Scenario_data!E4 &lt;Rubella!A5,Rubella!A5,Scenario_data!E4))</f>
-        <v>441303051.16330719</v>
+        <v>518976399.13094008</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">IF(F4&gt;Rubella!B6,Rubella!B6,IF(Scenario_data!F4 &lt;Rubella!A6,Rubella!A6,Scenario_data!F4))</f>
-        <v>518738648.8944546</v>
+        <v>642162313.27672553</v>
       </c>
       <c r="G17" s="7">
         <f ca="1">IF(G4&gt;Rubella!B7,Rubella!B7,IF(Scenario_data!G4 &lt;Rubella!A7,Rubella!A7,Scenario_data!G4))</f>
-        <v>560590321.12412798</v>
+        <v>718724385.09488463</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">IF(H4&gt;Rubella!B8,Rubella!B8,IF(Scenario_data!H4 &lt;Rubella!A8,Rubella!A8,Scenario_data!H4))</f>
-        <v>619263506.51350164</v>
+        <v>691224688.01780987</v>
       </c>
       <c r="I17" s="7">
         <f ca="1">IF(I4&gt;Rubella!B9,Rubella!B9,IF(Scenario_data!I4 &lt;Rubella!A9,Rubella!A9,Scenario_data!I4))</f>
-        <v>597953201.04888475</v>
+        <v>654650002.44740343</v>
       </c>
       <c r="J17" s="7">
         <f ca="1">IF(J4&gt;Rubella!B10,Rubella!B10,IF(Scenario_data!J4 &lt;Rubella!A10,Rubella!A10,Scenario_data!J4))</f>
-        <v>741556488.15382314</v>
+        <v>666920034.31631446</v>
       </c>
       <c r="K17" s="7">
         <f ca="1">IF(K4&gt;Rubella!B12=1,Rubella!B11,IF(Scenario_data!K4 &lt;Rubella!A11,Rubella!A11,Scenario_data!K4))</f>
-        <v>763885830.22618496</v>
+        <v>865825795.92512167</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -3757,43 +3753,43 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(B5&gt;Diphtheria!B2,Diphtheria!B2,IF(Scenario_data!B5 &lt;Diphtheria!A2,Diphtheria!A2,Scenario_data!B5))</f>
-        <v>742785491.46924627</v>
+        <v>677023497.45828068</v>
       </c>
       <c r="C18" s="7">
         <f ca="1">IF(C5&gt;Diphtheria!B3,Diphtheria!B3,IF(Scenario_data!C5 &lt;Diphtheria!A3,Diphtheria!A3,Scenario_data!C5))</f>
-        <v>752853587.4273622</v>
+        <v>683229740.30633855</v>
       </c>
       <c r="D18" s="7">
         <f ca="1">IF(D5&gt;Diphtheria!B4,Diphtheria!B4,IF(Scenario_data!D5 &lt;Diphtheria!A4,Diphtheria!A4,Scenario_data!D5))</f>
-        <v>846484448.36472392</v>
+        <v>817518417.19670308</v>
       </c>
       <c r="E18" s="7">
         <f ca="1">IF(E5&gt;Diphtheria!B5,Diphtheria!B5,IF(Scenario_data!E5 &lt;Diphtheria!A5,Diphtheria!A5,Scenario_data!E5))</f>
-        <v>911331567.75979292</v>
+        <v>890594656.53506279</v>
       </c>
       <c r="F18" s="7">
         <f ca="1">IF(F5&gt;Diphtheria!B6,Diphtheria!B6,IF(Scenario_data!F5 &lt;Diphtheria!A6,Diphtheria!A6,Scenario_data!F5))</f>
-        <v>904479481.78190124</v>
+        <v>939871879.58393037</v>
       </c>
       <c r="G18" s="7">
         <f ca="1">IF(G5&gt;Diphtheria!B7,Diphtheria!B7,IF(Scenario_data!G5 &lt;Diphtheria!A7,Diphtheria!A7,Scenario_data!G5))</f>
-        <v>1164816092.3500228</v>
+        <v>1163224184.0391212</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">IF(H5&gt;Diphtheria!B8,Diphtheria!B8,IF(Scenario_data!H5 &lt;Diphtheria!A8,Diphtheria!A8,Scenario_data!H5))</f>
-        <v>1458084052.6528018</v>
+        <v>1443366623.7817435</v>
       </c>
       <c r="I18" s="7">
         <f ca="1">IF(I5&gt;Diphtheria!B9,Diphtheria!B9,IF(Scenario_data!I5 &lt;Diphtheria!A9,Diphtheria!A9,Scenario_data!I5))</f>
-        <v>1527318076.5038919</v>
+        <v>1673641276.2313941</v>
       </c>
       <c r="J18" s="7">
         <f ca="1">IF(J5&gt;Diphtheria!B10,Diphtheria!B10,IF(Scenario_data!J5 &lt;Diphtheria!A10,Diphtheria!A10,Scenario_data!J5))</f>
-        <v>1591242235.5884593</v>
+        <v>1565260717.6774495</v>
       </c>
       <c r="K18" s="7">
         <f ca="1">IF(K5&gt;Diphtheria!B11,Diphtheria!B11,IF(Scenario_data!K5 &lt;Diphtheria!A11,Diphtheria!A11,Scenario_data!K5))</f>
-        <v>1920616477.7595139</v>
+        <v>1786830973.3253071</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -3802,43 +3798,43 @@
       </c>
       <c r="B19" s="7">
         <f ca="1">IF(B6&gt;Tetanus!B2,Tetanus!B2,IF(Scenario_data!B6 &lt;Tetanus!A2,Tetanus!A2,Scenario_data!B6))</f>
-        <v>602773484.32235479</v>
+        <v>671869414.68780088</v>
       </c>
       <c r="C19" s="7">
         <f ca="1">IF(C6&gt;Tetanus!B3,Tetanus!B3,IF(Scenario_data!C6 &lt;Tetanus!A3,Tetanus!A3,Scenario_data!C6))</f>
-        <v>640837760.7040205</v>
+        <v>678277910.89305747</v>
       </c>
       <c r="D19" s="7">
         <f ca="1">IF(D6&gt;Tetanus!B4,Tetanus!B4,IF(Scenario_data!D6 &lt;Tetanus!A4,Tetanus!A4,Scenario_data!D6))</f>
-        <v>685019527.58840501</v>
+        <v>640142293.25159991</v>
       </c>
       <c r="E19" s="7">
         <f ca="1">IF(E6&gt;Tetanus!B5,Tetanus!B5,IF(Scenario_data!E6 &lt;Tetanus!A5,Tetanus!A5,Scenario_data!E6))</f>
-        <v>628349818.47549438</v>
+        <v>660321107.94923842</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">IF(F6&gt;Tetanus!B6,Tetanus!B6,IF(Scenario_data!F6 &lt;Tetanus!A6,Tetanus!A6,Scenario_data!F6))</f>
-        <v>641662353.09790337</v>
+        <v>633614246.03202999</v>
       </c>
       <c r="G19" s="7">
         <f ca="1">IF(G6&gt;Tetanus!B7,Tetanus!B7,IF(Scenario_data!G6 &lt;Tetanus!A7,Tetanus!A7,Scenario_data!G6))</f>
-        <v>679487017.55810404</v>
+        <v>772317965.51780128</v>
       </c>
       <c r="H19" s="7">
         <f ca="1">IF(H6&gt;Tetanus!B8,Tetanus!B8,IF(Scenario_data!H6 &lt;Tetanus!A8,Tetanus!A8,Scenario_data!H6))</f>
-        <v>652578957.22678268</v>
+        <v>670874344.72589874</v>
       </c>
       <c r="I19" s="7">
         <f ca="1">IF(I6&gt;Tetanus!B9,Tetanus!B9,IF(Scenario_data!I6 &lt;Tetanus!A9,Tetanus!A9,Scenario_data!I6))</f>
-        <v>663703060.87461042</v>
+        <v>748693436.75190592</v>
       </c>
       <c r="J19" s="7">
         <f ca="1">IF(J6&gt;Tetanus!B10,Tetanus!B10,IF(Scenario_data!J6 &lt;Tetanus!A10,Tetanus!A10,Scenario_data!J6))</f>
-        <v>691493859.20329762</v>
+        <v>677967265.17084277</v>
       </c>
       <c r="K19" s="7">
         <f ca="1">IF(K6&gt;Tetanus!B11,Tetanus!B11,IF(Scenario_data!K6 &lt;Tetanus!A11,Tetanus!A11,Scenario_data!K6))</f>
-        <v>652692515.10939085</v>
+        <v>722016955.70364547</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -3847,43 +3843,43 @@
       </c>
       <c r="B20" s="7">
         <f ca="1">IF(B7&gt;Pertussis!B2,Pertussis!B2,IF(Scenario_data!B7 &lt;Pertussis!A2,Pertussis!A2,Scenario_data!B7))</f>
-        <v>362422627.99443895</v>
+        <v>377275718.16613919</v>
       </c>
       <c r="C20" s="7">
         <f ca="1">IF(C7&gt;Pertussis!B3,Pertussis!B3,IF(Scenario_data!C7 &lt;Pertussis!A3,Pertussis!A3,Scenario_data!C7))</f>
-        <v>315701250.17060524</v>
+        <v>372137409.08397961</v>
       </c>
       <c r="D20" s="7">
         <f ca="1">IF(D7&gt;Pertussis!B4,Pertussis!B4,IF(Scenario_data!D7 &lt;Pertussis!A4,Pertussis!A4,Scenario_data!D7))</f>
-        <v>368472445.85273087</v>
+        <v>348053062.2402299</v>
       </c>
       <c r="E20" s="7">
         <f ca="1">IF(E7&gt;Pertussis!B5,Pertussis!B5,IF(Scenario_data!E7 &lt;Pertussis!A5,Pertussis!A5,Scenario_data!E7))</f>
-        <v>317119649.02451921</v>
+        <v>360480876.08980185</v>
       </c>
       <c r="F20" s="7">
         <f ca="1">IF(F7&gt;Pertussis!B6,Pertussis!B6,IF(Scenario_data!F7 &lt;Pertussis!A6,Pertussis!A6,Scenario_data!F7))</f>
-        <v>376239025.84218717</v>
+        <v>331827976.45623082</v>
       </c>
       <c r="G20" s="7">
         <f ca="1">IF(G7&gt;Pertussis!B7,Pertussis!B7,IF(Scenario_data!G7 &lt;Pertussis!A7,Pertussis!A7,Scenario_data!G7))</f>
-        <v>374412379.16049558</v>
+        <v>330756169.81888652</v>
       </c>
       <c r="H20" s="7">
         <f ca="1">IF(H7&gt;Pertussis!B8,Pertussis!B8,IF(Scenario_data!H7 &lt;Pertussis!A8,Pertussis!A8,Scenario_data!H7))</f>
-        <v>356424154.96221793</v>
+        <v>360902134.27739215</v>
       </c>
       <c r="I20" s="7">
         <f ca="1">IF(I7&gt;Pertussis!B9,Pertussis!B9,IF(Scenario_data!I7 &lt;Pertussis!A9,Pertussis!A9,Scenario_data!I7))</f>
-        <v>387528371.29742432</v>
+        <v>388885875.51419872</v>
       </c>
       <c r="J20" s="7">
         <f ca="1">IF(J7&gt;Pertussis!B10,Pertussis!B10,IF(Scenario_data!J7 &lt;Pertussis!A10,Pertussis!A10,Scenario_data!J7))</f>
-        <v>357256293.51931</v>
+        <v>402237354.26486325</v>
       </c>
       <c r="K20" s="7">
         <f ca="1">IF(K7&gt;Pertussis!B11,Pertussis!B11,IF(Scenario_data!K7 &lt;Pertussis!A11,Pertussis!A11,Scenario_data!K7))</f>
-        <v>350848044.49634397</v>
+        <v>377135973.27511346</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -3892,43 +3888,43 @@
       </c>
       <c r="B21" s="7">
         <f ca="1">IF(B8&gt;Hepatitis_B!B2,Hepatitis_B!B2,IF(Scenario_data!B8 &lt;Hepatitis_B!A2,Hepatitis_B!A2,Scenario_data!B8))</f>
-        <v>395303027.42456394</v>
+        <v>375153099.97555006</v>
       </c>
       <c r="C21" s="7">
         <f ca="1">IF(C8&gt;Hepatitis_B!B3,Hepatitis_B!B3,IF(Scenario_data!C8 &lt;Hepatitis_B!A3,Hepatitis_B!A3,Scenario_data!C8))</f>
-        <v>408220393.14708143</v>
+        <v>399113630.95474243</v>
       </c>
       <c r="D21" s="7">
         <f ca="1">IF(D8&gt;Hepatitis_B!B4,Hepatitis_B!B4,IF(Scenario_data!D8 &lt;Hepatitis_B!A4,Hepatitis_B!A4,Scenario_data!D8))</f>
-        <v>444641915.07728684</v>
+        <v>359084337.29367602</v>
       </c>
       <c r="E21" s="7">
         <f ca="1">IF(E8&gt;Hepatitis_B!B5,Hepatitis_B!B5,IF(Scenario_data!E8 &lt;Hepatitis_B!A5,Hepatitis_B!A5,Scenario_data!E8))</f>
-        <v>453827503.85857785</v>
+        <v>421580866.27530158</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">IF(F8&gt;Hepatitis_B!B6,Hepatitis_B!B6,IF(Scenario_data!F8 &lt;Hepatitis_B!A6,Hepatitis_B!A6,Scenario_data!F8))</f>
-        <v>383013545.72927064</v>
+        <v>329371252.91806728</v>
       </c>
       <c r="G21" s="7">
         <f ca="1">IF(G8&gt;Hepatitis_B!B7,Hepatitis_B!B7,IF(Scenario_data!G8 &lt;Hepatitis_B!A7,Hepatitis_B!A7,Scenario_data!G8))</f>
-        <v>379502006.21421438</v>
+        <v>381002007.08612812</v>
       </c>
       <c r="H21" s="7">
         <f ca="1">IF(H8&gt;Hepatitis_B!B8,Hepatitis_B!B8,IF(Scenario_data!H8 &lt;Hepatitis_B!A8,Hepatitis_B!A8,Scenario_data!H8))</f>
-        <v>401255114.97082168</v>
+        <v>351949630.52484924</v>
       </c>
       <c r="I21" s="7">
         <f ca="1">IF(I8&gt;Hepatitis_B!B9,Hepatitis_B!B9,IF(Scenario_data!I8 &lt;Hepatitis_B!A9,Hepatitis_B!A9,Scenario_data!I8))</f>
-        <v>444774444.58579254</v>
+        <v>392146414.97037613</v>
       </c>
       <c r="J21" s="7">
         <f ca="1">IF(J8&gt;Hepatitis_B!B10,Hepatitis_B!B10,IF(Scenario_data!J8 &lt;Hepatitis_B!A10,Hepatitis_B!A10,Scenario_data!J8))</f>
-        <v>403463446.28985393</v>
+        <v>413178484.58318436</v>
       </c>
       <c r="K21" s="7">
         <f ca="1">IF(K8&gt;Hepatitis_B!B11,Hepatitis_B!B11,IF(Scenario_data!K8 &lt;Hepatitis_B!A11,Hepatitis_B!A11,Scenario_data!K8))</f>
-        <v>467796355.77015615</v>
+        <v>398402047.61702693</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -3937,43 +3933,43 @@
       </c>
       <c r="B22" s="7">
         <f ca="1">IF(B9&gt;Hib!B2,Hib!B2,IF(Scenario_data!B9 &lt;Hib!A2,Hib!A2,Scenario_data!B9))</f>
-        <v>314257258.63745034</v>
+        <v>321021498.77043068</v>
       </c>
       <c r="C22" s="7">
         <f ca="1">IF(C9&gt;Hib!B3,Hib!B3,IF(Scenario_data!C9 &lt;Hib!A3,Hib!A3,Scenario_data!C9))</f>
-        <v>314152799.93181235</v>
+        <v>324852068.52688533</v>
       </c>
       <c r="D22" s="7">
         <f ca="1">IF(D9&gt;Hib!B4,Hib!B4,IF(Scenario_data!D9 &lt;Hib!A4,Hib!A4,Scenario_data!D9))</f>
-        <v>350041789.64064449</v>
+        <v>333828730.00548226</v>
       </c>
       <c r="E22" s="7">
         <f ca="1">IF(E9&gt;Hib!B5,Hib!B5,IF(Scenario_data!E9 &lt;Hib!A5,Hib!A5,Scenario_data!E9))</f>
-        <v>301268334.68733639</v>
+        <v>329998445.03929907</v>
       </c>
       <c r="F22" s="7">
         <f ca="1">IF(F9&gt;Hib!B6,Hib!B6,IF(Scenario_data!F9 &lt;Hib!A6,Hib!A6,Scenario_data!F9))</f>
-        <v>352128748.55086374</v>
+        <v>374935935.10480356</v>
       </c>
       <c r="G22" s="7">
         <f ca="1">IF(G9&gt;Hib!B7,Hib!B7,IF(Scenario_data!G9 &lt;Hib!A7,Hib!A7,Scenario_data!G9))</f>
-        <v>355668888.58184254</v>
+        <v>374045908.13470089</v>
       </c>
       <c r="H22" s="7">
         <f ca="1">IF(H9&gt;Hib!B8,Hib!B8,IF(Scenario_data!H9 &lt;Hib!A8,Hib!A8,Scenario_data!H9))</f>
-        <v>398675396.96262902</v>
+        <v>387779792.11458975</v>
       </c>
       <c r="I22" s="7">
         <f ca="1">IF(I9&gt;Hib!B9,Hib!B9,IF(Scenario_data!I9 &lt;Hib!A9,Hib!A9,Scenario_data!I9))</f>
-        <v>427391965.79788744</v>
+        <v>389432695.59690118</v>
       </c>
       <c r="J22" s="7">
         <f ca="1">IF(J9&gt;Hib!B10,Hib!B10,IF(Scenario_data!J9 &lt;Hib!A10,Hib!A10,Scenario_data!J9))</f>
-        <v>352020151.85880196</v>
+        <v>395335860.46782255</v>
       </c>
       <c r="K22" s="7">
         <f ca="1">IF(K9&gt;Hib!B11,Hib!B11,IF(Scenario_data!K9 &lt;Hib!A11,Hib!A11,Scenario_data!K9))</f>
-        <v>434381232.9750579</v>
+        <v>441997400.83768731</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -3982,43 +3978,43 @@
       </c>
       <c r="B23" s="7">
         <f ca="1">IF(B10&gt;Polio!B2,Polio!B2,IF(Scenario_data!B10 &lt;Polio!A2,Polio!A2,Scenario_data!B10))</f>
-        <v>562510067.91676295</v>
+        <v>642257347.02621889</v>
       </c>
       <c r="C23" s="7">
         <f ca="1">IF(C10&gt;Polio!B3,Polio!B3,IF(Scenario_data!C10 &lt;Polio!A3,Polio!A3,Scenario_data!C10))</f>
-        <v>686050307.64316642</v>
+        <v>696375118.95304465</v>
       </c>
       <c r="D23" s="7">
         <f ca="1">IF(D10&gt;Polio!B4,Polio!B4,IF(Scenario_data!D10 &lt;Polio!A4,Polio!A4,Scenario_data!D10))</f>
-        <v>575413534.3232224</v>
+        <v>699522239.88239527</v>
       </c>
       <c r="E23" s="7">
         <f ca="1">IF(E10&gt;Polio!B5,Polio!B5,IF(Scenario_data!E10 &lt;Polio!A5,Polio!A5,Scenario_data!E10))</f>
-        <v>687383594.87407196</v>
+        <v>713196818.47858298</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">IF(F10&gt;Polio!B6,Polio!B6,IF(Scenario_data!F10 &lt;Polio!A6,Polio!A6,Scenario_data!F10))</f>
-        <v>697755472.33727348</v>
+        <v>685766669.14306688</v>
       </c>
       <c r="G23" s="7">
         <f ca="1">IF(G10&gt;Polio!B7,Polio!B7,IF(Scenario_data!G10 &lt;Polio!A7,Polio!A7,Scenario_data!G10))</f>
-        <v>780317577.12405515</v>
+        <v>894009291.88586974</v>
       </c>
       <c r="H23" s="7">
         <f ca="1">IF(H10&gt;Polio!B8,Polio!B8,IF(Scenario_data!H10 &lt;Polio!A8,Polio!A8,Scenario_data!H10))</f>
-        <v>749736107.30519927</v>
+        <v>777360922.36234915</v>
       </c>
       <c r="I23" s="7">
         <f ca="1">IF(I10&gt;Polio!B9,Polio!B9,IF(Scenario_data!I10 &lt;Polio!A9,Polio!A9,Scenario_data!I10))</f>
-        <v>870930380.34278071</v>
+        <v>917137512.60400784</v>
       </c>
       <c r="J23" s="7">
         <f ca="1">IF(J10&gt;Polio!B10,Polio!B10,IF(Scenario_data!J10 &lt;Polio!A10,Polio!A10,Scenario_data!J10))</f>
-        <v>907526188.16005743</v>
+        <v>846698697.37109864</v>
       </c>
       <c r="K23" s="7">
         <f ca="1">IF(K10&gt;Polio!B11,Polio!B11,IF(Scenario_data!K10 &lt;Polio!A11,Polio!A11,Scenario_data!K10))</f>
-        <v>892368067.98188782</v>
+        <v>888472934.35479891</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -4027,43 +4023,43 @@
       </c>
       <c r="B24" s="7">
         <f ca="1">IF(B11&gt;HPV!B2,HPV!B2,IF(Scenario_data!B11 &lt;HPV!A2,HPV!A2,Scenario_data!B11))</f>
-        <v>29375908.204356764</v>
+        <v>29941818.059163366</v>
       </c>
       <c r="C24" s="7">
         <f ca="1">IF(C11&gt;HPV!B3,HPV!B3,IF(Scenario_data!C11 &lt;HPV!A3,HPV!A3,Scenario_data!C11))</f>
-        <v>36973240.974811286</v>
+        <v>35945626.474653319</v>
       </c>
       <c r="D24" s="7">
         <f ca="1">IF(D11&gt;HPV!B4,HPV!B4,IF(Scenario_data!D11 &lt;HPV!A4,HPV!A4,Scenario_data!D11))</f>
-        <v>42810635.44118131</v>
+        <v>39295764.392632052</v>
       </c>
       <c r="E24" s="7">
         <f ca="1">IF(E11&gt;HPV!B5,HPV!B5,IF(Scenario_data!E11 &lt;HPV!A5,HPV!A5,Scenario_data!E11))</f>
-        <v>46450943.908866525</v>
+        <v>48422770.210406207</v>
       </c>
       <c r="F24" s="7">
         <f ca="1">IF(F11&gt;HPV!B6,HPV!B6,IF(Scenario_data!F11 &lt;HPV!A6,HPV!A6,Scenario_data!F11))</f>
-        <v>55751458.96213802</v>
+        <v>54601763.314007938</v>
       </c>
       <c r="G24" s="7">
         <f ca="1">IF(G11&gt;HPV!B7,HPV!B7,IF(Scenario_data!G11 &lt;HPV!A7,HPV!A7,Scenario_data!G11))</f>
-        <v>58567348.47724364</v>
+        <v>58092583.49952545</v>
       </c>
       <c r="H24" s="7">
         <f ca="1">IF(H11&gt;HPV!B8,HPV!B8,IF(Scenario_data!H11 &lt;HPV!A8,HPV!A8,Scenario_data!H11))</f>
-        <v>67149671.127208233</v>
+        <v>67108007.357160173</v>
       </c>
       <c r="I24" s="7">
         <f ca="1">IF(I11&gt;HPV!B9,HPV!B9,IF(Scenario_data!I11 &lt;HPV!A9,HPV!A9,Scenario_data!I11))</f>
-        <v>71955815.934473842</v>
+        <v>74338629.158265382</v>
       </c>
       <c r="J24" s="7">
         <f ca="1">IF(J11&gt;HPV!B10,HPV!B10,IF(Scenario_data!J11 &lt;HPV!A10,HPV!A10,Scenario_data!J11))</f>
-        <v>81054530.296169713</v>
+        <v>81068109.129203558</v>
       </c>
       <c r="K24" s="7">
         <f ca="1">IF(K11&gt;HPV!B11,HPV!B11,IF(Scenario_data!K11 &lt;HPV!A11,HPV!A11,Scenario_data!K11))</f>
-        <v>89313131.797970936</v>
+        <v>88939621.771273941</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -4072,43 +4068,43 @@
       </c>
       <c r="B25" s="7">
         <f ca="1">IF(B12&gt;Rotavirus!B2,Rotavirus!B2,IF(Scenario_data!B12 &lt;Rotavirus!A2,Rotavirus!A2,Scenario_data!B12))</f>
-        <v>225177168.58647105</v>
+        <v>209593325.68123284</v>
       </c>
       <c r="C25" s="7">
         <f ca="1">IF(C12&gt;Rotavirus!B3,Rotavirus!B3,IF(Scenario_data!C12 &lt;Rotavirus!A3,Rotavirus!A3,Scenario_data!C12))</f>
-        <v>211818559.40818676</v>
+        <v>195966077.850734</v>
       </c>
       <c r="D25" s="7">
         <f ca="1">IF(D12&gt;Rotavirus!B4,Rotavirus!B4,IF(Scenario_data!D12 &lt;Rotavirus!A4,Rotavirus!A4,Scenario_data!D12))</f>
-        <v>197255863.65012899</v>
+        <v>227277618.646478</v>
       </c>
       <c r="E25" s="7">
         <f ca="1">IF(E12&gt;Rotavirus!B5,Rotavirus!B5,IF(Scenario_data!E12 &lt;Rotavirus!A5,Rotavirus!A5,Scenario_data!E12))</f>
-        <v>292473628.34834433</v>
+        <v>259852058.96648291</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">IF(F12&gt;Rotavirus!B6,Rotavirus!B6,IF(Scenario_data!F12 &lt;Rotavirus!A6,Rotavirus!A6,Scenario_data!F12))</f>
-        <v>338275388.45804477</v>
+        <v>322776130.15048355</v>
       </c>
       <c r="G25" s="7">
         <f ca="1">IF(G12&gt;Rotavirus!B7,Rotavirus!B7,IF(Scenario_data!G12 &lt;Rotavirus!A7,Rotavirus!A7,Scenario_data!G12))</f>
-        <v>381248305.86100721</v>
+        <v>346186034.79188496</v>
       </c>
       <c r="H25" s="7">
         <f ca="1">IF(H12&gt;Rotavirus!B8,Rotavirus!B8,IF(Scenario_data!H12 &lt;Rotavirus!A8,Rotavirus!A8,Scenario_data!H12))</f>
-        <v>444205575.87645489</v>
+        <v>462262560.34396815</v>
       </c>
       <c r="I25" s="7">
         <f ca="1">IF(I12&gt;Rotavirus!B9,Rotavirus!B9,IF(Scenario_data!I12 &lt;Rotavirus!A9,Rotavirus!A9,Scenario_data!I12))</f>
-        <v>529896172.87651294</v>
+        <v>517488113.05277401</v>
       </c>
       <c r="J25" s="7">
         <f ca="1">IF(J12&gt;Rotavirus!B10,Rotavirus!B10,IF(Scenario_data!J12 &lt;Rotavirus!A10,Rotavirus!A10,Scenario_data!J12))</f>
-        <v>663705067.16484177</v>
+        <v>609537918.88273335</v>
       </c>
       <c r="K25" s="7">
         <f ca="1">IF(K12&gt;Rotavirus!B11,Rotavirus!B11,IF(Scenario_data!K12 &lt;Rotavirus!A11,Rotavirus!A11,Scenario_data!K12))</f>
-        <v>735092352.48062396</v>
+        <v>714702627.20747411</v>
       </c>
       <c r="M25" s="4"/>
     </row>
@@ -4118,43 +4114,43 @@
       </c>
       <c r="B26" s="7">
         <f ca="1">IF(B13&gt;PCV!B2,PCV!B2,IF(Scenario_data!B13 &lt;PCV!A2,PCV!A2,Scenario_data!B13))</f>
-        <v>241071149.45158824</v>
+        <v>232765581.05368111</v>
       </c>
       <c r="C26" s="7">
         <f ca="1">IF(C13&gt;PCV!B3,PCV!B3,IF(Scenario_data!C13 &lt;PCV!A3,PCV!A3,Scenario_data!C13))</f>
-        <v>254015380.07613316</v>
+        <v>253540537.92330924</v>
       </c>
       <c r="D26" s="7">
         <f ca="1">IF(D13&gt;PCV!B4,PCV!B4,IF(Scenario_data!D13 &lt;PCV!A4,PCV!A4,Scenario_data!D13))</f>
-        <v>290306034.27144468</v>
+        <v>274389553.50016904</v>
       </c>
       <c r="E26" s="7">
         <f ca="1">IF(E13&gt;PCV!B5,PCV!B5,IF(Scenario_data!E13 &lt;PCV!A5,PCV!A5,Scenario_data!E13))</f>
-        <v>306939644.52600533</v>
+        <v>309079668.52331275</v>
       </c>
       <c r="F26" s="7">
         <f ca="1">IF(F13&gt;PCV!B6,PCV!B6,IF(Scenario_data!F13 &lt;PCV!A6,PCV!A6,Scenario_data!F13))</f>
-        <v>336686422.01807326</v>
+        <v>347500177.60982418</v>
       </c>
       <c r="G26" s="7">
         <f ca="1">IF(G13&gt;PCV!B7,PCV!B7,IF(Scenario_data!G13 &lt;PCV!A7,PCV!A7,Scenario_data!G13))</f>
-        <v>369304271.70029795</v>
+        <v>374213031.4678508</v>
       </c>
       <c r="H26" s="7">
         <f ca="1">IF(H13&gt;PCV!B8,PCV!B8,IF(Scenario_data!H13 &lt;PCV!A8,PCV!A8,Scenario_data!H13))</f>
-        <v>410655800.2244851</v>
+        <v>394696124.35456306</v>
       </c>
       <c r="I26" s="7">
         <f ca="1">IF(I13&gt;PCV!B9,PCV!B9,IF(Scenario_data!I13 &lt;PCV!A9,PCV!A9,Scenario_data!I13))</f>
-        <v>442999496.19893312</v>
+        <v>459739135.39224821</v>
       </c>
       <c r="J26" s="7">
         <f ca="1">IF(J13&gt;PCV!B10,PCV!B10,IF(Scenario_data!J13 &lt;PCV!A10,PCV!A10,Scenario_data!J13))</f>
-        <v>475584022.34082985</v>
+        <v>490499877.32620466</v>
       </c>
       <c r="K26" s="7">
         <f ca="1">IF(K13&gt;PCV!B11,PCV!B11,IF(Scenario_data!K13 &lt;PCV!A11,PCV!A11,Scenario_data!K13))</f>
-        <v>454731642.6732856</v>
+        <v>421602194.88334519</v>
       </c>
       <c r="M26" s="4"/>
     </row>
